--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Malešice/Databaze Malešice 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Malešice/Databaze Malešice 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4992" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5068" uniqueCount="382">
   <si>
     <t>Datum</t>
   </si>
@@ -481,6 +481,21 @@
     <t>19.05.2026</t>
   </si>
   <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 30 s</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>12 min 16 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -923,9 +938,6 @@
   </si>
   <si>
     <t>15.02.2026</t>
-  </si>
-  <si>
-    <t>20:30</t>
   </si>
   <si>
     <t>16 min 16 s</t>
@@ -5575,6 +5587,431 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M123" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M124" s="3">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P125" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q125" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R125" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S125" s="3">
+        <v>15962.0</v>
+      </c>
+      <c r="T125" s="3">
+        <v>5753.0</v>
+      </c>
+      <c r="U125" s="3">
+        <v>7844.0</v>
+      </c>
+      <c r="V125" s="3">
+        <v>7314.0</v>
+      </c>
+      <c r="W125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y125" s="3">
+        <v>4970.0</v>
+      </c>
+      <c r="AA125" s="3">
+        <v>1083.0</v>
+      </c>
+      <c r="AB125" s="3">
+        <v>43926.4</v>
+      </c>
+      <c r="AC125" s="3">
+        <v>-0.4000000000014552</v>
+      </c>
+      <c r="AD125" s="3">
+        <v>0.3264651454985113</v>
+      </c>
+      <c r="AE125" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AI125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ125" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK125" s="3">
+        <v>674.0</v>
+      </c>
+      <c r="AL125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM125" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO125" s="3">
+        <v>113.0</v>
+      </c>
+      <c r="AP125" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="AQ125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU125" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV125" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M129" s="3">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M130" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q132" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R132" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S132" s="3">
+        <v>15666.2</v>
+      </c>
+      <c r="T132" s="3">
+        <v>7433.0</v>
+      </c>
+      <c r="U132" s="3">
+        <v>10683.0</v>
+      </c>
+      <c r="V132" s="3">
+        <v>6406.0</v>
+      </c>
+      <c r="W132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X132" s="3">
+        <v>1027.0</v>
+      </c>
+      <c r="Y132" s="3">
+        <v>3066.0</v>
+      </c>
+      <c r="AA132" s="3">
+        <v>3991.0</v>
+      </c>
+      <c r="AB132" s="3">
+        <v>47844.2</v>
+      </c>
+      <c r="AC132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD132" s="3">
+        <v>0.28445588387361076</v>
+      </c>
+      <c r="AE132" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="AH132" s="3">
+        <v>99.0</v>
+      </c>
+      <c r="AI132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ132" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK132" s="3">
+        <v>119.0</v>
+      </c>
+      <c r="AL132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM132" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO132" s="3">
+        <v>122.0</v>
+      </c>
+      <c r="AP132" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="AQ132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU132" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV132" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5735,7 +6172,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -5755,7 +6192,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>106</v>
@@ -5775,7 +6212,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>106</v>
@@ -5795,7 +6232,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
@@ -5818,7 +6255,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>106</v>
@@ -5841,7 +6278,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>106</v>
@@ -5904,7 +6341,7 @@
         <v>3.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AN7" s="3">
         <v>0.0</v>
@@ -5936,7 +6373,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>112</v>
@@ -5956,7 +6393,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>112</v>
@@ -5976,7 +6413,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>112</v>
@@ -5999,7 +6436,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>112</v>
@@ -6059,7 +6496,7 @@
         <v>4.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -6091,7 +6528,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -6111,7 +6548,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -6131,7 +6568,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -6154,7 +6591,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -6177,7 +6614,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -6200,7 +6637,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -6263,7 +6700,7 @@
         <v>2.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AN17" s="3">
         <v>0.0</v>
@@ -6295,7 +6732,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>73</v>
@@ -6315,7 +6752,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>73</v>
@@ -6335,7 +6772,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>73</v>
@@ -6347,10 +6784,10 @@
         <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>89</v>
@@ -6358,7 +6795,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>73</v>
@@ -6387,7 +6824,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>73</v>
@@ -6410,7 +6847,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>73</v>
@@ -6470,7 +6907,7 @@
         <v>0.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AN23" s="3">
         <v>1.0</v>
@@ -6502,7 +6939,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>83</v>
@@ -6522,7 +6959,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>83</v>
@@ -6542,7 +6979,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>83</v>
@@ -6565,7 +7002,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>83</v>
@@ -6594,7 +7031,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>83</v>
@@ -6657,7 +7094,7 @@
         <v>0.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -6689,7 +7126,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>92</v>
@@ -6709,7 +7146,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
@@ -6729,7 +7166,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
@@ -6752,7 +7189,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -6781,7 +7218,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
@@ -6844,7 +7281,7 @@
         <v>3.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -6876,7 +7313,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>98</v>
@@ -6896,7 +7333,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>98</v>
@@ -6916,7 +7353,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>98</v>
@@ -6936,7 +7373,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>98</v>
@@ -6965,7 +7402,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>98</v>
@@ -6988,7 +7425,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -7057,7 +7494,7 @@
         <v>1.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -7089,7 +7526,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>106</v>
@@ -7109,7 +7546,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>106</v>
@@ -7129,7 +7566,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>106</v>
@@ -7152,7 +7589,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>106</v>
@@ -7175,7 +7612,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -7238,7 +7675,7 @@
         <v>2.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AN44" s="3">
         <v>0.0</v>
@@ -7270,7 +7707,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>112</v>
@@ -7290,7 +7727,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>112</v>
@@ -7310,7 +7747,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>112</v>
@@ -7333,7 +7770,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>112</v>
@@ -7396,7 +7833,7 @@
         <v>2.0</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AN48" s="3">
         <v>0.0</v>
@@ -7428,7 +7865,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -7448,7 +7885,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -7468,7 +7905,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -7488,7 +7925,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -7511,7 +7948,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -7540,7 +7977,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -7563,7 +8000,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -7626,7 +8063,7 @@
         <v>0.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -7658,7 +8095,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>73</v>
@@ -7678,7 +8115,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>73</v>
@@ -7698,7 +8135,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>73</v>
@@ -7718,7 +8155,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>73</v>
@@ -7738,7 +8175,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>73</v>
@@ -7765,7 +8202,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>73</v>
@@ -7798,7 +8235,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>73</v>
@@ -7856,7 +8293,7 @@
         <v>2.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -7888,7 +8325,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>83</v>
@@ -7908,7 +8345,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>83</v>
@@ -7928,7 +8365,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>83</v>
@@ -7951,7 +8388,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>83</v>
@@ -8017,7 +8454,7 @@
         <v>2.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AN66" s="3">
         <v>0.0</v>
@@ -8049,7 +8486,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>92</v>
@@ -8069,7 +8506,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>92</v>
@@ -8089,7 +8526,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>92</v>
@@ -8109,7 +8546,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>92</v>
@@ -8132,7 +8569,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>92</v>
@@ -8161,7 +8598,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>92</v>
@@ -8173,7 +8610,7 @@
         <v>99</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>102</v>
@@ -8181,7 +8618,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>92</v>
@@ -8241,7 +8678,7 @@
         <v>3.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AN73" s="3">
         <v>1.0</v>
@@ -8273,7 +8710,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>98</v>
@@ -8293,7 +8730,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>98</v>
@@ -8313,7 +8750,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>98</v>
@@ -8333,7 +8770,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>98</v>
@@ -8362,7 +8799,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>98</v>
@@ -8385,7 +8822,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>98</v>
@@ -8448,7 +8885,7 @@
         <v>3.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -8480,7 +8917,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>106</v>
@@ -8500,7 +8937,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>106</v>
@@ -8520,7 +8957,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>106</v>
@@ -8540,7 +8977,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>106</v>
@@ -8563,7 +9000,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>106</v>
@@ -8586,7 +9023,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>106</v>
@@ -8655,7 +9092,7 @@
         <v>4.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -8687,7 +9124,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>112</v>
@@ -8707,7 +9144,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>112</v>
@@ -8727,7 +9164,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>112</v>
@@ -8747,7 +9184,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>112</v>
@@ -8776,7 +9213,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>112</v>
@@ -8799,7 +9236,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>112</v>
@@ -8862,7 +9299,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -8894,7 +9331,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
@@ -8914,7 +9351,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -8934,7 +9371,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -8954,7 +9391,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>49</v>
@@ -8983,7 +9420,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -9006,7 +9443,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -9029,7 +9466,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -9092,7 +9529,7 @@
         <v>1.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN98" s="3">
         <v>1.0</v>
@@ -9124,7 +9561,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>73</v>
@@ -9144,7 +9581,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>73</v>
@@ -9164,7 +9601,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>73</v>
@@ -9184,7 +9621,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>73</v>
@@ -9204,7 +9641,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>73</v>
@@ -9224,7 +9661,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>73</v>
@@ -9251,7 +9688,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>73</v>
@@ -9264,7 +9701,7 @@
         <v>80</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>93</v>
@@ -9278,7 +9715,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>73</v>
@@ -9348,7 +9785,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -9380,7 +9817,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>83</v>
@@ -9400,7 +9837,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>83</v>
@@ -9420,7 +9857,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>83</v>
@@ -9440,7 +9877,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>83</v>
@@ -9463,7 +9900,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>83</v>
@@ -9486,7 +9923,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>83</v>
@@ -9552,7 +9989,7 @@
         <v>2.0</v>
       </c>
       <c r="AM112" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AN112" s="3">
         <v>0.0</v>
@@ -9584,7 +10021,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>92</v>
@@ -9604,7 +10041,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>92</v>
@@ -9624,7 +10061,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>92</v>
@@ -9644,7 +10081,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>92</v>
@@ -9667,7 +10104,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>92</v>
@@ -9727,7 +10164,7 @@
         <v>2.0</v>
       </c>
       <c r="AM117" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AN117" s="3">
         <v>0.0</v>
@@ -9759,7 +10196,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>98</v>
@@ -9779,7 +10216,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>98</v>
@@ -9799,7 +10236,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>98</v>
@@ -9819,7 +10256,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>98</v>
@@ -9848,7 +10285,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>98</v>
@@ -9871,7 +10308,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>98</v>
@@ -9931,7 +10368,7 @@
         <v>2.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -9963,7 +10400,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>106</v>
@@ -9983,7 +10420,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>106</v>
@@ -10003,7 +10440,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>106</v>
@@ -10023,7 +10460,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>106</v>
@@ -10046,7 +10483,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>106</v>
@@ -10069,7 +10506,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>106</v>
@@ -10132,7 +10569,7 @@
         <v>0.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AN129" s="3">
         <v>0.0</v>
@@ -10164,7 +10601,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>112</v>
@@ -10184,7 +10621,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>112</v>
@@ -10204,7 +10641,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>112</v>
@@ -10224,7 +10661,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>112</v>
@@ -10247,7 +10684,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>112</v>
@@ -10270,7 +10707,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>112</v>
@@ -10330,7 +10767,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AN135" s="3">
         <v>0.0</v>
@@ -10362,7 +10799,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>49</v>
@@ -10382,7 +10819,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>49</v>
@@ -10402,7 +10839,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>49</v>
@@ -10422,7 +10859,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -10451,7 +10888,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
@@ -10474,7 +10911,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -10531,7 +10968,7 @@
         <v>2.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN141" s="3">
         <v>1.0</v>
@@ -10563,7 +11000,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>73</v>
@@ -10583,7 +11020,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>73</v>
@@ -10603,7 +11040,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>73</v>
@@ -10623,7 +11060,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>73</v>
@@ -10643,7 +11080,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>73</v>
@@ -10672,7 +11109,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>73</v>
@@ -10764,7 +11201,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>83</v>
@@ -10784,7 +11221,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>83</v>
@@ -10804,7 +11241,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>83</v>
@@ -10824,7 +11261,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>83</v>
@@ -10844,7 +11281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>83</v>
@@ -10873,7 +11310,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>83</v>
@@ -10896,7 +11333,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>83</v>
@@ -10962,7 +11399,7 @@
         <v>0.0</v>
       </c>
       <c r="AM154" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AN154" s="3">
         <v>1.0</v>
@@ -10994,7 +11431,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>92</v>
@@ -11014,7 +11451,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>92</v>
@@ -11034,7 +11471,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>92</v>
@@ -11057,7 +11494,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>92</v>
@@ -11111,7 +11548,7 @@
         <v>1.0</v>
       </c>
       <c r="AM158" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AN158" s="3">
         <v>0.0</v>
@@ -11143,7 +11580,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>98</v>
@@ -11163,7 +11600,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>98</v>
@@ -11183,7 +11620,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>98</v>
@@ -11206,7 +11643,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>98</v>
@@ -11235,7 +11672,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>98</v>
@@ -11295,7 +11732,7 @@
         <v>3.0</v>
       </c>
       <c r="AM163" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="AN163" s="3">
         <v>1.0</v>
@@ -11327,7 +11764,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>106</v>
@@ -11347,7 +11784,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>106</v>
@@ -11367,7 +11804,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>106</v>
@@ -11387,7 +11824,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>106</v>
@@ -11410,7 +11847,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>106</v>
@@ -11439,7 +11876,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>106</v>
@@ -11502,7 +11939,7 @@
         <v>1.0</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AN169" s="3">
         <v>1.0</v>
@@ -11534,7 +11971,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>112</v>
@@ -11554,7 +11991,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>112</v>
@@ -11574,7 +12011,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>112</v>
@@ -11594,7 +12031,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>112</v>
@@ -11614,7 +12051,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>112</v>
@@ -11637,7 +12074,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>112</v>
@@ -11660,7 +12097,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>112</v>
@@ -11723,7 +12160,7 @@
         <v>2.0</v>
       </c>
       <c r="AM176" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AN176" s="3">
         <v>0.0</v>
@@ -11913,7 +12350,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>83</v>
@@ -11933,7 +12370,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>83</v>
@@ -11953,7 +12390,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>83</v>
@@ -11973,7 +12410,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>83</v>
@@ -12002,7 +12439,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>83</v>
@@ -12025,7 +12462,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>83</v>
@@ -12120,7 +12557,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>92</v>
@@ -12140,7 +12577,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>92</v>
@@ -12160,7 +12597,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>92</v>
@@ -12183,7 +12620,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>92</v>
@@ -12212,13 +12649,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>51</v>
@@ -12241,7 +12678,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>92</v>
@@ -12304,7 +12741,7 @@
         <v>2.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -12336,7 +12773,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>98</v>
@@ -12356,7 +12793,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>98</v>
@@ -12376,13 +12813,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -12405,7 +12842,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>98</v>
@@ -12428,7 +12865,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>98</v>
@@ -12488,7 +12925,7 @@
         <v>1.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -12520,7 +12957,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>106</v>
@@ -12540,7 +12977,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>106</v>
@@ -12560,7 +12997,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>106</v>
@@ -12580,7 +13017,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>106</v>
@@ -12603,7 +13040,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>106</v>
@@ -12660,7 +13097,7 @@
         <v>1.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AN23" s="3">
         <v>0.0</v>
@@ -12692,7 +13129,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>112</v>
@@ -12712,7 +13149,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>112</v>
@@ -12732,7 +13169,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>112</v>
@@ -12761,7 +13198,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>112</v>
@@ -12784,7 +13221,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>112</v>
@@ -12844,7 +13281,7 @@
         <v>0.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -12876,7 +13313,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>49</v>
@@ -12896,7 +13333,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -12916,7 +13353,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -12936,7 +13373,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
@@ -12965,7 +13402,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -12988,7 +13425,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -13051,7 +13488,7 @@
         <v>3.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AN34" s="3">
         <v>1.0</v>
@@ -13083,7 +13520,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>73</v>
@@ -13103,7 +13540,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>73</v>
@@ -13123,7 +13560,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>73</v>
@@ -13143,7 +13580,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>73</v>
@@ -13166,7 +13603,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>73</v>
@@ -13195,7 +13632,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>73</v>
@@ -13218,7 +13655,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>73</v>
@@ -13275,7 +13712,7 @@
         <v>1.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -13307,7 +13744,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>83</v>
@@ -13327,7 +13764,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>83</v>
@@ -13347,7 +13784,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>83</v>
@@ -13367,7 +13804,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>83</v>
@@ -13390,7 +13827,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>83</v>
@@ -13413,7 +13850,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>83</v>
@@ -13476,7 +13913,7 @@
         <v>3.0</v>
       </c>
       <c r="AM47" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AN47" s="3">
         <v>0.0</v>
@@ -13508,7 +13945,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>92</v>
@@ -13528,7 +13965,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>92</v>
@@ -13548,7 +13985,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>92</v>
@@ -13560,7 +13997,7 @@
         <v>61</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>59</v>
@@ -13571,7 +14008,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>92</v>
@@ -13580,7 +14017,7 @@
         <v>63</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>148</v>
@@ -13600,13 +14037,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>51</v>
@@ -13629,7 +14066,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>92</v>
@@ -13689,7 +14126,7 @@
         <v>1.0</v>
       </c>
       <c r="AM53" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AN53" s="3">
         <v>2.0</v>
@@ -13721,7 +14158,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>98</v>
@@ -13741,7 +14178,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>98</v>
@@ -13761,7 +14198,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>98</v>
@@ -13781,7 +14218,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>98</v>
@@ -13810,7 +14247,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>98</v>
@@ -13833,7 +14270,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>98</v>
@@ -13893,7 +14330,7 @@
         <v>2.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN59" s="3">
         <v>1.0</v>
@@ -13925,7 +14362,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>106</v>
@@ -13945,7 +14382,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>106</v>
@@ -13965,7 +14402,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>106</v>
@@ -13974,7 +14411,7 @@
         <v>108</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>79</v>
@@ -13985,7 +14422,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>106</v>
@@ -14008,7 +14445,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>106</v>
@@ -14031,7 +14468,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>106</v>
@@ -14094,7 +14531,7 @@
         <v>0.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AN65" s="3">
         <v>0.0</v>
@@ -14126,7 +14563,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>112</v>
@@ -14146,7 +14583,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>112</v>
@@ -14166,7 +14603,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>112</v>
@@ -14186,7 +14623,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>112</v>
@@ -14209,7 +14646,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>112</v>
@@ -14266,7 +14703,7 @@
         <v>2.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AN70" s="3">
         <v>0.0</v>
@@ -14298,7 +14735,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
@@ -14318,7 +14755,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -14338,7 +14775,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -14358,7 +14795,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
@@ -14387,7 +14824,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -14410,7 +14847,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
@@ -14467,7 +14904,7 @@
         <v>2.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -14499,7 +14936,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>73</v>
@@ -14519,7 +14956,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>73</v>
@@ -14539,7 +14976,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>73</v>
@@ -14559,7 +14996,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>73</v>
@@ -14582,7 +15019,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>73</v>
@@ -14605,7 +15042,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>73</v>
@@ -14668,7 +15105,7 @@
         <v>1.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AN82" s="3">
         <v>0.0</v>
@@ -14700,7 +15137,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>83</v>
@@ -14720,7 +15157,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>83</v>
@@ -14740,7 +15177,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>83</v>
@@ -14760,7 +15197,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>83</v>
@@ -14783,7 +15220,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>83</v>
@@ -14806,7 +15243,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>83</v>
@@ -14869,7 +15306,7 @@
         <v>0.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -14901,7 +15338,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>92</v>
@@ -14921,7 +15358,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>92</v>
@@ -14941,7 +15378,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>92</v>
@@ -14964,7 +15401,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>92</v>
@@ -15021,7 +15458,7 @@
         <v>1.0</v>
       </c>
       <c r="AM92" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AN92" s="3">
         <v>0.0</v>
@@ -15053,7 +15490,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>98</v>
@@ -15073,7 +15510,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>98</v>
@@ -15093,7 +15530,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>98</v>
@@ -15116,7 +15553,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>98</v>
@@ -15139,7 +15576,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>98</v>
@@ -15202,7 +15639,7 @@
         <v>1.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -15234,7 +15671,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>106</v>
@@ -15254,7 +15691,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
@@ -15274,7 +15711,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -15303,7 +15740,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>106</v>
@@ -15326,7 +15763,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>106</v>
@@ -15389,7 +15826,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -15421,7 +15858,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>112</v>
@@ -15441,7 +15878,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>112</v>
@@ -15461,7 +15898,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>112</v>
@@ -15481,7 +15918,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
@@ -15504,7 +15941,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>112</v>
@@ -15527,7 +15964,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>112</v>
@@ -15587,7 +16024,7 @@
         <v>2.0</v>
       </c>
       <c r="AM108" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AN108" s="3">
         <v>0.0</v>
@@ -15619,7 +16056,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>49</v>
@@ -15639,7 +16076,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -15648,7 +16085,7 @@
         <v>75</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>64</v>
@@ -15659,7 +16096,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
@@ -15679,7 +16116,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -15702,7 +16139,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
@@ -15725,7 +16162,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -15788,7 +16225,7 @@
         <v>5.0</v>
       </c>
       <c r="AM114" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AN114" s="3">
         <v>0.0</v>
@@ -15820,7 +16257,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>73</v>
@@ -15840,7 +16277,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>73</v>
@@ -15860,7 +16297,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>73</v>
@@ -15880,7 +16317,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>73</v>
@@ -15900,7 +16337,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>73</v>
@@ -15927,7 +16364,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>73</v>
@@ -15954,7 +16391,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>73</v>
@@ -16024,7 +16461,7 @@
         <v>2.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AN121" s="3">
         <v>0.0</v>
@@ -16056,7 +16493,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>83</v>
@@ -16076,7 +16513,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>83</v>
@@ -16096,7 +16533,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>83</v>
@@ -16116,7 +16553,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>83</v>
@@ -16136,7 +16573,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>83</v>
@@ -16165,7 +16602,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>83</v>
@@ -16188,7 +16625,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>83</v>
@@ -16251,7 +16688,7 @@
         <v>1.0</v>
       </c>
       <c r="AM128" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AN128" s="3">
         <v>1.0</v>
@@ -16283,7 +16720,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>92</v>
@@ -16303,7 +16740,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>92</v>
@@ -16323,7 +16760,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>92</v>
@@ -16346,7 +16783,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>92</v>
@@ -16375,7 +16812,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>92</v>
@@ -16432,7 +16869,7 @@
         <v>0.0</v>
       </c>
       <c r="AM133" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AN133" s="3">
         <v>1.0</v>
@@ -16464,7 +16901,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>98</v>
@@ -16484,7 +16921,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>98</v>
@@ -16504,7 +16941,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>98</v>
@@ -16524,7 +16961,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>98</v>
@@ -16547,7 +16984,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>98</v>
@@ -16576,7 +17013,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>98</v>
@@ -16636,7 +17073,7 @@
         <v>1.0</v>
       </c>
       <c r="AM139" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AN139" s="3">
         <v>1.0</v>
@@ -16668,7 +17105,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>106</v>
@@ -16688,7 +17125,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>106</v>
@@ -16708,7 +17145,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>106</v>
@@ -16731,7 +17168,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>106</v>
@@ -16754,7 +17191,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>106</v>
@@ -16811,7 +17248,7 @@
         <v>1.0</v>
       </c>
       <c r="AM144" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AN144" s="3">
         <v>0.0</v>
@@ -16843,7 +17280,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>112</v>
@@ -16863,7 +17300,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>112</v>
@@ -16883,7 +17320,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>112</v>
@@ -16903,7 +17340,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>112</v>
@@ -16926,7 +17363,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>112</v>
@@ -16949,7 +17386,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>112</v>
@@ -17009,7 +17446,7 @@
         <v>1.0</v>
       </c>
       <c r="AM150" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AN150" s="3">
         <v>0.0</v>
@@ -17041,7 +17478,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -17061,7 +17498,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
@@ -17081,7 +17518,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -17101,7 +17538,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -17110,7 +17547,7 @@
         <v>63</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>79</v>
@@ -17130,7 +17567,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -17153,7 +17590,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -17251,7 +17688,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>73</v>
@@ -17263,7 +17700,7 @@
         <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>117</v>
@@ -17271,7 +17708,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>73</v>
@@ -17291,7 +17728,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>73</v>
@@ -17311,7 +17748,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>73</v>
@@ -17334,7 +17771,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>73</v>
@@ -17357,7 +17794,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>73</v>
@@ -17420,7 +17857,7 @@
         <v>0.0</v>
       </c>
       <c r="AM162" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AN162" s="3">
         <v>0.0</v>
@@ -17452,7 +17889,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>83</v>
@@ -17472,7 +17909,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>83</v>
@@ -17492,7 +17929,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>83</v>
@@ -17515,7 +17952,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>83</v>
@@ -17538,7 +17975,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>83</v>
@@ -17601,7 +18038,7 @@
         <v>1.0</v>
       </c>
       <c r="AM167" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN167" s="3">
         <v>0.0</v>
@@ -17633,7 +18070,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>92</v>
@@ -17653,7 +18090,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>92</v>
@@ -17673,7 +18110,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>92</v>
@@ -17696,7 +18133,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>92</v>
@@ -17725,7 +18162,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>92</v>
@@ -17788,7 +18225,7 @@
         <v>0.0</v>
       </c>
       <c r="AM172" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AN172" s="3">
         <v>1.0</v>
@@ -17820,7 +18257,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>98</v>
@@ -17832,7 +18269,7 @@
         <v>53</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>117</v>
@@ -17840,7 +18277,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>98</v>
@@ -17860,7 +18297,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>98</v>
@@ -17880,7 +18317,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>98</v>
@@ -17903,7 +18340,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>98</v>
@@ -17932,7 +18369,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>98</v>
@@ -17992,7 +18429,7 @@
         <v>0.0</v>
       </c>
       <c r="AM178" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AN178" s="3">
         <v>1.0</v>
@@ -18193,7 +18630,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>83</v>
@@ -18213,7 +18650,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>83</v>
@@ -18233,7 +18670,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>83</v>
@@ -18253,7 +18690,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>83</v>
@@ -18276,7 +18713,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>83</v>
@@ -18305,7 +18742,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>83</v>
@@ -18371,7 +18808,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -18403,7 +18840,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>92</v>
@@ -18423,13 +18860,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>61</v>
@@ -18452,7 +18889,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>92</v>
@@ -18472,7 +18909,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>92</v>
@@ -18495,7 +18932,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>92</v>
@@ -18549,7 +18986,7 @@
         <v>1.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AN12" s="3">
         <v>1.0</v>
@@ -18581,7 +19018,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>98</v>
@@ -18601,7 +19038,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>98</v>
@@ -18624,13 +19061,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>51</v>
@@ -18653,7 +19090,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>98</v>
@@ -18707,7 +19144,7 @@
         <v>4.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN16" s="3">
         <v>1.0</v>
@@ -18739,7 +19176,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>106</v>
@@ -18759,7 +19196,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>106</v>
@@ -18782,7 +19219,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>106</v>
@@ -18802,7 +19239,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>106</v>
@@ -18825,7 +19262,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>106</v>
@@ -18888,7 +19325,7 @@
         <v>1.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AN21" s="3">
         <v>0.0</v>
@@ -18920,7 +19357,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>112</v>
@@ -18940,7 +19377,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>112</v>
@@ -18960,7 +19397,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>112</v>
@@ -18980,7 +19417,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>112</v>
@@ -19003,7 +19440,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>112</v>
@@ -19069,7 +19506,7 @@
         <v>4.0</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AN26" s="3">
         <v>0.0</v>
@@ -19101,7 +19538,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>49</v>
@@ -19121,7 +19558,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>49</v>
@@ -19141,7 +19578,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>49</v>
@@ -19161,7 +19598,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -19181,7 +19618,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -19208,7 +19645,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
@@ -19235,7 +19672,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -19296,7 +19733,7 @@
         <v>4.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AN33" s="3">
         <v>0.0</v>
@@ -19328,7 +19765,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>73</v>
@@ -19348,7 +19785,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>73</v>
@@ -19368,7 +19805,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>73</v>
@@ -19388,7 +19825,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>73</v>
@@ -19408,13 +19845,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>51</v>
@@ -19437,7 +19874,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>73</v>
@@ -19460,7 +19897,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>73</v>
@@ -19520,7 +19957,7 @@
         <v>5.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AN40" s="3">
         <v>1.0</v>
@@ -19552,7 +19989,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>83</v>
@@ -19572,7 +20009,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>83</v>
@@ -19592,7 +20029,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>83</v>
@@ -19615,7 +20052,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>83</v>
@@ -19638,7 +20075,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>83</v>
@@ -19727,7 +20164,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>92</v>
@@ -19747,7 +20184,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
@@ -19767,7 +20204,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>92</v>
@@ -19790,7 +20227,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>92</v>
@@ -19819,7 +20256,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>92</v>
@@ -19876,7 +20313,7 @@
         <v>3.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -19908,7 +20345,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>98</v>
@@ -19928,7 +20365,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>98</v>
@@ -19948,7 +20385,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>98</v>
@@ -19971,7 +20408,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>98</v>
@@ -19994,7 +20431,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>98</v>
@@ -20060,7 +20497,7 @@
         <v>7.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AN55" s="3">
         <v>0.0</v>
@@ -20092,7 +20529,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>106</v>
@@ -20112,7 +20549,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>106</v>
@@ -20132,7 +20569,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>106</v>
@@ -20155,7 +20592,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>106</v>
@@ -20178,7 +20615,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>106</v>
@@ -20244,7 +20681,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AN60" s="3">
         <v>0.0</v>
@@ -20276,7 +20713,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>112</v>
@@ -20296,7 +20733,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>112</v>
@@ -20316,7 +20753,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>112</v>
@@ -20339,13 +20776,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -20368,7 +20805,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>112</v>
@@ -20425,7 +20862,7 @@
         <v>0.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -20457,7 +20894,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -20477,7 +20914,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -20497,13 +20934,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>51</v>
@@ -20517,7 +20954,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
@@ -20546,7 +20983,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -20569,7 +21006,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
@@ -20592,7 +21029,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -20655,7 +21092,7 @@
         <v>10.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -20687,7 +21124,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>73</v>
@@ -20707,7 +21144,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>73</v>
@@ -20727,7 +21164,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>73</v>
@@ -20747,7 +21184,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>73</v>
@@ -20774,7 +21211,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>73</v>
@@ -20784,7 +21221,7 @@
       <c r="E77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>130</v>
@@ -20807,7 +21244,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>73</v>
@@ -20874,7 +21311,7 @@
         <v>3.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -20906,7 +21343,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>83</v>
@@ -20926,7 +21363,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>83</v>
@@ -20946,7 +21383,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>83</v>
@@ -20958,7 +21395,7 @@
         <v>55</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>302</v>
+        <v>157</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>124</v>
@@ -20966,7 +21403,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>83</v>
@@ -20989,7 +21426,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>83</v>
@@ -21012,7 +21449,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>83</v>
@@ -21041,7 +21478,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>83</v>
@@ -21104,7 +21541,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -21136,7 +21573,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -21156,7 +21593,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>92</v>
@@ -21176,7 +21613,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>92</v>
@@ -21199,13 +21636,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>89</v>
@@ -21228,7 +21665,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>92</v>
@@ -21291,7 +21728,7 @@
         <v>2.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -21323,7 +21760,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>98</v>
@@ -21343,7 +21780,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -21363,7 +21800,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>98</v>
@@ -21386,7 +21823,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>98</v>
@@ -21415,7 +21852,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>98</v>
@@ -21507,7 +21944,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>106</v>
@@ -21519,7 +21956,7 @@
         <v>53</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>128</v>
@@ -21527,7 +21964,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>106</v>
@@ -21547,7 +21984,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>106</v>
@@ -21567,7 +22004,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
@@ -21590,7 +22027,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -21613,7 +22050,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>106</v>
@@ -21673,7 +22110,7 @@
         <v>2.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AN101" s="3">
         <v>0.0</v>
@@ -21705,7 +22142,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>112</v>
@@ -21725,7 +22162,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>112</v>
@@ -21745,7 +22182,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>112</v>
@@ -21765,7 +22202,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>112</v>
@@ -21788,13 +22225,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>51</v>
@@ -21817,7 +22254,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>112</v>
@@ -21880,7 +22317,7 @@
         <v>2.0</v>
       </c>
       <c r="AM107" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AN107" s="3">
         <v>1.0</v>
@@ -21912,7 +22349,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>49</v>
@@ -21932,7 +22369,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>49</v>
@@ -21952,7 +22389,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -21975,7 +22412,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
@@ -21998,13 +22435,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -22027,7 +22464,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
@@ -22087,7 +22524,7 @@
         <v>1.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN113" s="3">
         <v>1.0</v>
@@ -22119,7 +22556,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>73</v>
@@ -22139,7 +22576,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>73</v>
@@ -22159,7 +22596,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>73</v>
@@ -22179,7 +22616,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>73</v>
@@ -22202,7 +22639,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>73</v>
@@ -22225,7 +22662,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>73</v>
@@ -22291,7 +22728,7 @@
         <v>6.0</v>
       </c>
       <c r="AM119" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AN119" s="3">
         <v>0.0</v>
@@ -22323,7 +22760,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>83</v>
@@ -22343,7 +22780,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>83</v>
@@ -22363,7 +22800,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>83</v>
@@ -22383,13 +22820,13 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>51</v>
@@ -22412,7 +22849,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>83</v>
@@ -22435,7 +22872,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>83</v>
@@ -22530,7 +22967,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>92</v>
@@ -22550,7 +22987,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>92</v>
@@ -22562,7 +22999,7 @@
         <v>66</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>70</v>
@@ -22570,7 +23007,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>92</v>
@@ -22593,7 +23030,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>92</v>
@@ -22622,7 +23059,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>92</v>
@@ -22685,7 +23122,7 @@
         <v>1.0</v>
       </c>
       <c r="AM130" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AN130" s="3">
         <v>1.0</v>
@@ -22717,7 +23154,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>98</v>
@@ -22737,7 +23174,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>98</v>
@@ -22757,7 +23194,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>98</v>
@@ -22769,7 +23206,7 @@
         <v>130</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>122</v>
@@ -22777,7 +23214,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>98</v>
@@ -22806,13 +23243,13 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>51</v>
@@ -22835,7 +23272,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>98</v>
@@ -22895,7 +23332,7 @@
         <v>1.0</v>
       </c>
       <c r="AM136" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AN136" s="3">
         <v>2.0</v>
@@ -22927,7 +23364,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>106</v>
@@ -22947,7 +23384,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>106</v>
@@ -22967,7 +23404,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>106</v>
@@ -22990,7 +23427,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>106</v>
@@ -23013,7 +23450,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>106</v>
@@ -23076,7 +23513,7 @@
         <v>0.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AN141" s="3">
         <v>0.0</v>
@@ -23108,7 +23545,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>112</v>
@@ -23128,7 +23565,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>112</v>
@@ -23148,7 +23585,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>112</v>
@@ -23160,7 +23597,7 @@
         <v>51</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>70</v>
@@ -23168,7 +23605,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>112</v>
@@ -23191,7 +23628,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>112</v>
@@ -23214,7 +23651,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>112</v>
@@ -23274,7 +23711,7 @@
         <v>1.0</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AN147" s="3">
         <v>0.0</v>
@@ -23306,7 +23743,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>49</v>
@@ -23326,7 +23763,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>49</v>
@@ -23346,7 +23783,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>49</v>
@@ -23358,7 +23795,7 @@
         <v>88</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>132</v>
@@ -23366,7 +23803,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -23389,13 +23826,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>51</v>
@@ -23418,7 +23855,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -23441,7 +23878,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -23504,7 +23941,7 @@
         <v>2.0</v>
       </c>
       <c r="AM154" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AN154" s="3">
         <v>1.0</v>
@@ -23536,7 +23973,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>73</v>
@@ -23556,7 +23993,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>73</v>
@@ -23576,13 +24013,13 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>51</v>
@@ -23605,7 +24042,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>73</v>
@@ -23628,7 +24065,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>73</v>
@@ -23648,7 +24085,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>73</v>
@@ -23901,7 +24338,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>112</v>
@@ -23921,7 +24358,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>112</v>
@@ -23941,7 +24378,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>112</v>
@@ -23961,7 +24398,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>112</v>
@@ -23981,7 +24418,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>112</v>
@@ -24004,7 +24441,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>112</v>
@@ -24027,7 +24464,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>112</v>
@@ -24090,7 +24527,7 @@
         <v>5.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN8" s="3">
         <v>0.0</v>
@@ -24122,7 +24559,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -24142,13 +24579,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>51</v>
@@ -24162,7 +24599,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -24182,7 +24619,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -24205,7 +24642,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -24228,7 +24665,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -24251,7 +24688,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -24263,7 +24700,7 @@
         <v>50</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="S15" s="3">
         <v>16534.0</v>
@@ -24314,7 +24751,7 @@
         <v>3.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AN15" s="3">
         <v>0.0</v>
@@ -24346,7 +24783,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>73</v>
@@ -24366,7 +24803,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>73</v>
@@ -24386,7 +24823,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>73</v>
@@ -24406,7 +24843,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>73</v>
@@ -24426,7 +24863,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>73</v>
@@ -24449,7 +24886,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>73</v>
@@ -24472,7 +24909,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>73</v>
@@ -24538,7 +24975,7 @@
         <v>4.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -24570,7 +25007,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>83</v>
@@ -24590,13 +25027,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>53</v>
@@ -24610,7 +25047,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>83</v>
@@ -24630,7 +25067,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>83</v>
@@ -24653,7 +25090,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>83</v>
@@ -24682,7 +25119,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>83</v>
@@ -24691,7 +25128,7 @@
         <v>8.0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>75</v>
@@ -24742,7 +25179,7 @@
         <v>6.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -24774,7 +25211,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>92</v>
@@ -24794,7 +25231,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
@@ -24814,7 +25251,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
@@ -24834,7 +25271,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -24857,13 +25294,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>51</v>
@@ -24886,7 +25323,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>92</v>
@@ -24943,7 +25380,7 @@
         <v>3.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AN34" s="3">
         <v>1.0</v>
@@ -24975,7 +25412,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>98</v>
@@ -24995,7 +25432,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>98</v>
@@ -25015,7 +25452,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>98</v>
@@ -25035,13 +25472,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -25055,7 +25492,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -25078,13 +25515,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>51</v>
@@ -25107,7 +25544,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>98</v>
@@ -25170,7 +25607,7 @@
         <v>3.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -25202,7 +25639,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>106</v>
@@ -25222,13 +25659,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>53</v>
@@ -25242,7 +25679,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -25265,7 +25702,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>106</v>
@@ -25277,7 +25714,7 @@
         <v>51</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>70</v>
@@ -25294,7 +25731,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>106</v>
@@ -25354,7 +25791,7 @@
         <v>3.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AN46" s="3">
         <v>1.0</v>
@@ -25386,7 +25823,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>112</v>
@@ -25406,7 +25843,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>112</v>
@@ -25426,7 +25863,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>112</v>
@@ -25449,13 +25886,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>51</v>
@@ -25478,7 +25915,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>112</v>
@@ -25507,7 +25944,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>112</v>
@@ -25570,7 +26007,7 @@
         <v>12.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AN52" s="3">
         <v>2.0</v>
@@ -25602,7 +26039,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -25622,7 +26059,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -25642,7 +26079,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -25665,7 +26102,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>49</v>
@@ -25688,13 +26125,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>51</v>
@@ -25717,7 +26154,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>49</v>
@@ -25783,7 +26220,7 @@
         <v>9.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AN58" s="3">
         <v>1.0</v>
@@ -25815,7 +26252,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>73</v>
@@ -25835,7 +26272,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>73</v>
@@ -25855,7 +26292,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>73</v>
@@ -25875,7 +26312,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>73</v>
@@ -25895,7 +26332,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>73</v>
@@ -25918,7 +26355,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>73</v>
@@ -25947,7 +26384,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>73</v>
@@ -26010,7 +26447,7 @@
         <v>6.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -26042,7 +26479,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>83</v>
@@ -26062,7 +26499,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>83</v>
@@ -26082,13 +26519,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>53</v>
@@ -26102,7 +26539,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>83</v>
@@ -26122,7 +26559,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>83</v>
@@ -26149,7 +26586,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>83</v>
@@ -26176,7 +26613,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>83</v>
@@ -26189,7 +26626,7 @@
         <v>2.0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R72" s="1" t="s">
         <v>75</v>
@@ -26246,7 +26683,7 @@
         <v>4.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AN72" s="3">
         <v>0.0</v>
@@ -26278,7 +26715,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>92</v>
@@ -26298,7 +26735,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>92</v>
@@ -26318,7 +26755,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>92</v>
@@ -26338,7 +26775,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>92</v>
@@ -26358,7 +26795,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>92</v>
@@ -26381,7 +26818,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>92</v>
@@ -26410,7 +26847,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>92</v>
@@ -26476,7 +26913,7 @@
         <v>5.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -26508,7 +26945,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>98</v>
@@ -26528,7 +26965,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>98</v>
@@ -26548,7 +26985,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>98</v>
@@ -26571,13 +27008,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>51</v>
@@ -26594,7 +27031,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>98</v>
@@ -26657,7 +27094,7 @@
         <v>5.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN84" s="3">
         <v>0.0</v>
@@ -26689,7 +27126,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>106</v>
@@ -26709,13 +27146,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>53</v>
@@ -26729,7 +27166,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>106</v>
@@ -26752,7 +27189,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>106</v>
@@ -26775,7 +27212,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>106</v>
@@ -26784,7 +27221,7 @@
         <v>2.0</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>75</v>
@@ -26841,7 +27278,7 @@
         <v>2.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AN89" s="3">
         <v>0.0</v>
@@ -26873,7 +27310,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>112</v>
@@ -26893,7 +27330,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>112</v>
@@ -26913,13 +27350,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>53</v>
@@ -26933,7 +27370,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>112</v>
@@ -26966,7 +27403,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>112</v>
@@ -26993,7 +27430,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>112</v>
@@ -27006,7 +27443,7 @@
         <v>1.0</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>54</v>
@@ -27060,7 +27497,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AN95" s="3">
         <v>1.0</v>
@@ -27092,7 +27529,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -27112,7 +27549,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -27132,13 +27569,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>53</v>
@@ -27152,7 +27589,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -27161,10 +27598,10 @@
         <v>54</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>124</v>
@@ -27172,7 +27609,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -27195,13 +27632,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>51</v>
@@ -27224,7 +27661,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
@@ -27247,7 +27684,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>49</v>
@@ -27256,7 +27693,7 @@
         <v>4.0</v>
       </c>
       <c r="Q103" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>75</v>
@@ -27310,7 +27747,7 @@
         <v>14.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AN103" s="3">
         <v>1.0</v>
@@ -27342,7 +27779,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>73</v>
@@ -27362,7 +27799,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>73</v>
@@ -27382,13 +27819,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>61</v>
@@ -27402,7 +27839,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>73</v>
@@ -27422,7 +27859,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>73</v>
@@ -27442,7 +27879,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>73</v>
@@ -27465,13 +27902,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>51</v>
@@ -27494,7 +27931,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>73</v>
@@ -27503,7 +27940,7 @@
         <v>3.0</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>75</v>
@@ -27557,7 +27994,7 @@
         <v>3.0</v>
       </c>
       <c r="AM111" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AN111" s="3">
         <v>1.0</v>
@@ -27589,7 +28026,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>83</v>
@@ -27609,7 +28046,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>83</v>
@@ -27629,7 +28066,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>83</v>
@@ -27649,7 +28086,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>83</v>
@@ -27672,7 +28109,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>83</v>
@@ -27695,7 +28132,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>83</v>
@@ -27755,7 +28192,7 @@
         <v>5.0</v>
       </c>
       <c r="AM117" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN117" s="3">
         <v>0.0</v>
@@ -27787,7 +28224,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>92</v>
@@ -27807,7 +28244,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>92</v>
@@ -27827,7 +28264,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>92</v>
@@ -27847,7 +28284,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>92</v>
@@ -27867,7 +28304,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>92</v>
@@ -27890,7 +28327,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>92</v>
@@ -27919,7 +28356,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>92</v>
@@ -27982,7 +28419,7 @@
         <v>1.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AN124" s="3">
         <v>1.0</v>
@@ -28014,7 +28451,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>98</v>
@@ -28034,13 +28471,13 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>53</v>
@@ -28054,7 +28491,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>98</v>
@@ -28077,13 +28514,13 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>51</v>
@@ -28106,7 +28543,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>98</v>
@@ -28115,7 +28552,7 @@
         <v>7.0</v>
       </c>
       <c r="Q129" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>75</v>
@@ -28169,7 +28606,7 @@
         <v>1.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="AN129" s="3">
         <v>1.0</v>
@@ -28201,13 +28638,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>53</v>
@@ -28221,7 +28658,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>106</v>
@@ -28241,7 +28678,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>106</v>
@@ -28264,7 +28701,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>106</v>
@@ -28324,7 +28761,7 @@
         <v>3.0</v>
       </c>
       <c r="AM133" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AN133" s="3">
         <v>0.0</v>
@@ -28356,7 +28793,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>112</v>
@@ -28376,7 +28813,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>112</v>
@@ -28396,7 +28833,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>112</v>
@@ -28419,7 +28856,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>112</v>
@@ -28448,7 +28885,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>112</v>
@@ -28511,7 +28948,7 @@
         <v>6.0</v>
       </c>
       <c r="AM138" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AN138" s="3">
         <v>1.0</v>
@@ -28543,7 +28980,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -28563,13 +29000,13 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>53</v>
@@ -28583,7 +29020,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -28603,13 +29040,13 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>51</v>
@@ -28623,7 +29060,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>49</v>
@@ -28646,7 +29083,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>49</v>
@@ -28669,7 +29106,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>49</v>
@@ -28729,7 +29166,7 @@
         <v>7.0</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AN145" s="3">
         <v>0.0</v>
@@ -28761,7 +29198,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>73</v>
@@ -28781,7 +29218,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>73</v>
@@ -28801,13 +29238,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>53</v>
@@ -28821,7 +29258,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>73</v>
@@ -28836,7 +29273,7 @@
         <v>113</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>77</v>
@@ -28844,7 +29281,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>73</v>
@@ -28867,13 +29304,13 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>51</v>
@@ -28896,7 +29333,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>73</v>
@@ -28919,7 +29356,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>73</v>
@@ -28928,7 +29365,7 @@
         <v>2.0</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>75</v>
@@ -29014,7 +29451,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>83</v>
@@ -29034,7 +29471,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>83</v>
@@ -29054,13 +29491,13 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>61</v>
@@ -29074,7 +29511,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>83</v>
@@ -29097,7 +29534,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>83</v>
@@ -29120,7 +29557,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>83</v>
@@ -29140,7 +29577,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>83</v>
@@ -29149,7 +29586,7 @@
         <v>0.0</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R160" s="1" t="s">
         <v>75</v>
@@ -29206,7 +29643,7 @@
         <v>0.0</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AN160" s="3">
         <v>0.0</v>
@@ -29238,7 +29675,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>92</v>
@@ -29258,7 +29695,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>92</v>
@@ -29270,7 +29707,7 @@
         <v>53</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>128</v>
@@ -29278,7 +29715,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>92</v>
@@ -29298,7 +29735,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>92</v>
@@ -29321,7 +29758,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>92</v>
@@ -29344,7 +29781,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>92</v>
@@ -29407,7 +29844,7 @@
         <v>1.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AN166" s="3">
         <v>0.0</v>
@@ -29439,7 +29876,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>98</v>
@@ -29459,7 +29896,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>98</v>
@@ -29479,7 +29916,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>98</v>
@@ -29499,7 +29936,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>98</v>
@@ -29522,7 +29959,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>98</v>
@@ -29582,7 +30019,7 @@
         <v>0.0</v>
       </c>
       <c r="AM171" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN171" s="3">
         <v>0.0</v>
@@ -29614,7 +30051,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>106</v>
@@ -29626,7 +30063,7 @@
         <v>53</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>128</v>
@@ -29634,7 +30071,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>106</v>
@@ -29654,7 +30091,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>106</v>
@@ -29663,7 +30100,7 @@
         <v>108</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>95</v>
@@ -29674,7 +30111,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>106</v>
@@ -29697,7 +30134,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>106</v>
@@ -29720,13 +30157,13 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>106</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I177" s="2" t="s">
         <v>51</v>
@@ -29749,7 +30186,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>106</v>
@@ -29809,7 +30246,7 @@
         <v>0.0</v>
       </c>
       <c r="AM178" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AN178" s="3">
         <v>1.0</v>
@@ -29841,7 +30278,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>112</v>
@@ -29861,7 +30298,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>112</v>
@@ -29881,7 +30318,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>112</v>
@@ -29904,13 +30341,13 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I182" s="2" t="s">
         <v>51</v>
@@ -29933,7 +30370,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>112</v>
@@ -29962,7 +30399,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>112</v>
@@ -30016,7 +30453,7 @@
         <v>2.0</v>
       </c>
       <c r="AM184" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AN184" s="3">
         <v>2.0</v>
@@ -30048,7 +30485,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>49</v>
@@ -30068,7 +30505,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>49</v>
@@ -30088,13 +30525,13 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>53</v>
@@ -30108,7 +30545,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>49</v>
@@ -30131,7 +30568,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>49</v>
@@ -30160,7 +30597,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>49</v>
@@ -30169,7 +30606,7 @@
         <v>1.0</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="S190" s="3">
         <v>20932.0</v>
@@ -30255,7 +30692,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>73</v>
@@ -30275,7 +30712,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>73</v>
@@ -30295,7 +30732,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>73</v>
@@ -30315,7 +30752,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>73</v>
@@ -30338,7 +30775,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>73</v>
@@ -30361,7 +30798,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>73</v>
@@ -30424,7 +30861,7 @@
         <v>3.0</v>
       </c>
       <c r="AM196" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AN196" s="3">
         <v>0.0</v>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Malešice/Databaze Malešice 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Malešice/Databaze Malešice 2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5068" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="396">
   <si>
     <t>Datum</t>
   </si>
@@ -496,6 +496,66 @@
     <t>12 min 16 s</t>
   </si>
   <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>13 min 54 s</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 14 s</t>
+  </si>
+  <si>
+    <t>24.05.2026</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>12 min 53 s</t>
+  </si>
+  <si>
+    <t>25.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 01 s</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>15 min 25 s</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 05 s</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>18 min 28 s</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>15 min 21 s</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
+  </si>
+  <si>
+    <t>12 min 45 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -559,9 +619,6 @@
     <t>10.04.2026</t>
   </si>
   <si>
-    <t>12 min 45 s</t>
-  </si>
-  <si>
     <t>11.04.2026</t>
   </si>
   <si>
@@ -577,9 +634,6 @@
     <t>13.04.2026</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
     <t>11 min 48 s</t>
   </si>
   <si>
@@ -607,18 +661,12 @@
     <t>18.04.2026</t>
   </si>
   <si>
-    <t>19:00</t>
-  </si>
-  <si>
     <t>11 min 07 s</t>
   </si>
   <si>
     <t>19.04.2026</t>
   </si>
   <si>
-    <t>11 min 14 s</t>
-  </si>
-  <si>
     <t>20.04.2026</t>
   </si>
   <si>
@@ -913,9 +961,6 @@
     <t>11.02.2026</t>
   </si>
   <si>
-    <t>11 min 01 s</t>
-  </si>
-  <si>
     <t>12.02.2026</t>
   </si>
   <si>
@@ -1031,9 +1076,6 @@
   </si>
   <si>
     <t>06.01.2026</t>
-  </si>
-  <si>
-    <t>12 min 53 s</t>
   </si>
   <si>
     <t>07.01.2026</t>
@@ -6012,6 +6054,1900 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M136" s="3">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="P137" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="Q137" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R137" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S137" s="3">
+        <v>23420.3</v>
+      </c>
+      <c r="T137" s="3">
+        <v>13889.0</v>
+      </c>
+      <c r="U137" s="3">
+        <v>15007.0</v>
+      </c>
+      <c r="V137" s="3">
+        <v>10568.0</v>
+      </c>
+      <c r="W137" s="3">
+        <v>872.1</v>
+      </c>
+      <c r="X137" s="3">
+        <v>2152.0</v>
+      </c>
+      <c r="Y137" s="3">
+        <v>7566.0</v>
+      </c>
+      <c r="AA137" s="3">
+        <v>1434.0</v>
+      </c>
+      <c r="AB137" s="3">
+        <v>75755.90000000001</v>
+      </c>
+      <c r="AC137" s="3">
+        <v>0.4999999999854481</v>
+      </c>
+      <c r="AD137" s="3">
+        <v>0.15886310562247702</v>
+      </c>
+      <c r="AE137" s="3">
+        <v>1500.0</v>
+      </c>
+      <c r="AH137" s="3">
+        <v>1500.0</v>
+      </c>
+      <c r="AI137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ137" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK137" s="3">
+        <v>733.0</v>
+      </c>
+      <c r="AL137" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AM137" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO137" s="3">
+        <v>174.0</v>
+      </c>
+      <c r="AP137" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="AQ137" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS137" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="AT137" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU137" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="AV137" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M142" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="N142" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O142" s="3">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M143" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M144" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N144" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O144" s="3">
+        <v>225.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P145" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="Q145" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R145" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S145" s="3">
+        <v>25549.0</v>
+      </c>
+      <c r="T145" s="3">
+        <v>8886.0</v>
+      </c>
+      <c r="U145" s="3">
+        <v>13421.0</v>
+      </c>
+      <c r="V145" s="3">
+        <v>10879.2</v>
+      </c>
+      <c r="W145" s="3">
+        <v>514.0</v>
+      </c>
+      <c r="X145" s="3">
+        <v>1774.0</v>
+      </c>
+      <c r="Y145" s="3">
+        <v>4574.0</v>
+      </c>
+      <c r="AA145" s="3">
+        <v>250.0</v>
+      </c>
+      <c r="AB145" s="3">
+        <v>70338.59999999999</v>
+      </c>
+      <c r="AC145" s="3">
+        <v>-0.39999999999417923</v>
+      </c>
+      <c r="AD145" s="3">
+        <v>0.24724523955873173</v>
+      </c>
+      <c r="AE145" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AH145" s="3">
+        <v>4500.0</v>
+      </c>
+      <c r="AI145" s="3">
+        <v>765.0</v>
+      </c>
+      <c r="AJ145" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AK145" s="3">
+        <v>1703.0</v>
+      </c>
+      <c r="AL145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM145" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AN145" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO145" s="3">
+        <v>173.0</v>
+      </c>
+      <c r="AP145" s="3">
+        <v>23.0</v>
+      </c>
+      <c r="AQ145" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AR145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU145" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV145" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M149" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="N149" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O149" s="3">
+        <v>720.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L150" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M150" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L151" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M151" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P152" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="Q152" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R152" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S152" s="3">
+        <v>18635.0</v>
+      </c>
+      <c r="T152" s="3">
+        <v>9037.0</v>
+      </c>
+      <c r="U152" s="3">
+        <v>12870.0</v>
+      </c>
+      <c r="V152" s="3">
+        <v>13022.1</v>
+      </c>
+      <c r="W152" s="3">
+        <v>1096.0</v>
+      </c>
+      <c r="X152" s="3">
+        <v>593.0</v>
+      </c>
+      <c r="Y152" s="3">
+        <v>3532.0</v>
+      </c>
+      <c r="AA152" s="3">
+        <v>173.0</v>
+      </c>
+      <c r="AB152" s="3">
+        <v>63586.1</v>
+      </c>
+      <c r="AC152" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD152" s="3">
+        <v>0.2849697479044289</v>
+      </c>
+      <c r="AE152" s="3">
+        <v>501.0</v>
+      </c>
+      <c r="AH152" s="3">
+        <v>4000.0</v>
+      </c>
+      <c r="AI152" s="3">
+        <v>720.0</v>
+      </c>
+      <c r="AJ152" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK152" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL152" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="AM152" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN152" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO152" s="3">
+        <v>151.0</v>
+      </c>
+      <c r="AP152" s="3">
+        <v>31.0</v>
+      </c>
+      <c r="AQ152" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AR152" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AS152" s="3">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="AT152" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU152" s="3">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AV152" s="3">
+        <v>0.06451612903225806</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M155" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="N155" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O155" s="3">
+        <v>405.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M156" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="P157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q157" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R157" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S157" s="3">
+        <v>11037.0</v>
+      </c>
+      <c r="T157" s="3">
+        <v>8020.0</v>
+      </c>
+      <c r="U157" s="3">
+        <v>5695.0</v>
+      </c>
+      <c r="V157" s="3">
+        <v>6663.0</v>
+      </c>
+      <c r="W157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X157" s="3">
+        <v>1386.0</v>
+      </c>
+      <c r="Y157" s="3">
+        <v>4085.0</v>
+      </c>
+      <c r="AA157" s="3">
+        <v>2823.0</v>
+      </c>
+      <c r="AB157" s="3">
+        <v>39487.0</v>
+      </c>
+      <c r="AC157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD157" s="3">
+        <v>0.37716758890839536</v>
+      </c>
+      <c r="AH157" s="3">
+        <v>759.0</v>
+      </c>
+      <c r="AI157" s="3">
+        <v>405.0</v>
+      </c>
+      <c r="AJ157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL157" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM157" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN157" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO157" s="3">
+        <v>109.0</v>
+      </c>
+      <c r="AP157" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="AQ157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS157" s="3">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AT157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU157" s="3">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AV157" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P162" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="Q162" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R162" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S162" s="3">
+        <v>15626.0</v>
+      </c>
+      <c r="T162" s="3">
+        <v>4625.0</v>
+      </c>
+      <c r="U162" s="3">
+        <v>7733.0</v>
+      </c>
+      <c r="V162" s="3">
+        <v>7821.2</v>
+      </c>
+      <c r="W162" s="3">
+        <v>329.0</v>
+      </c>
+      <c r="X162" s="3">
+        <v>1141.0</v>
+      </c>
+      <c r="Y162" s="3">
+        <v>3106.0</v>
+      </c>
+      <c r="AA162" s="3">
+        <v>3873.0</v>
+      </c>
+      <c r="AB162" s="3">
+        <v>43113.2</v>
+      </c>
+      <c r="AC162" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD162" s="3">
+        <v>0.34689495725730884</v>
+      </c>
+      <c r="AI162" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ162" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK162" s="3">
+        <v>219.0</v>
+      </c>
+      <c r="AL162" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM162" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AN162" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO162" s="3">
+        <v>106.0</v>
+      </c>
+      <c r="AP162" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="AQ162" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AR162" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS162" s="3">
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="AT162" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AU162" s="3">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="AV162" s="3">
+        <v>0.17647058823529413</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M166" s="3">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P167" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q167" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R167" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S167" s="3">
+        <v>12378.0</v>
+      </c>
+      <c r="T167" s="3">
+        <v>2985.0</v>
+      </c>
+      <c r="U167" s="3">
+        <v>7775.0</v>
+      </c>
+      <c r="V167" s="3">
+        <v>7636.0</v>
+      </c>
+      <c r="W167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X167" s="3">
+        <v>1957.0</v>
+      </c>
+      <c r="Y167" s="3">
+        <v>4495.0</v>
+      </c>
+      <c r="AA167" s="3">
+        <v>3019.0</v>
+      </c>
+      <c r="AB167" s="3">
+        <v>39288.0</v>
+      </c>
+      <c r="AC167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD167" s="3">
+        <v>0.26533745894995436</v>
+      </c>
+      <c r="AE167" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AI167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ167" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AK167" s="3">
+        <v>394.0</v>
+      </c>
+      <c r="AL167" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM167" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AN167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO167" s="3">
+        <v>109.0</v>
+      </c>
+      <c r="AP167" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="AQ167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS167" s="3">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AT167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU167" s="3">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AV167" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M170" s="3">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M171" s="3">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P172" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="Q172" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R172" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S172" s="3">
+        <v>15576.0</v>
+      </c>
+      <c r="T172" s="3">
+        <v>4669.0</v>
+      </c>
+      <c r="U172" s="3">
+        <v>10765.0</v>
+      </c>
+      <c r="V172" s="3">
+        <v>11852.0</v>
+      </c>
+      <c r="W172" s="3">
+        <v>1274.0</v>
+      </c>
+      <c r="X172" s="3">
+        <v>399.0</v>
+      </c>
+      <c r="Y172" s="3">
+        <v>3644.0</v>
+      </c>
+      <c r="AA172" s="3">
+        <v>9204.0</v>
+      </c>
+      <c r="AB172" s="3">
+        <v>56984.0</v>
+      </c>
+      <c r="AC172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD172" s="3">
+        <v>0.23811882814870505</v>
+      </c>
+      <c r="AI172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL172" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM172" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AN172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO172" s="3">
+        <v>127.0</v>
+      </c>
+      <c r="AP172" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="AQ172" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS172" s="3">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AT172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU172" s="3">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AV172" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L177" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M177" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J178" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M178" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M179" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P180" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="Q180" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R180" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S180" s="3">
+        <v>15117.0</v>
+      </c>
+      <c r="T180" s="3">
+        <v>6541.0</v>
+      </c>
+      <c r="U180" s="3">
+        <v>17910.0</v>
+      </c>
+      <c r="V180" s="3">
+        <v>11059.2</v>
+      </c>
+      <c r="W180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X180" s="3">
+        <v>1974.0</v>
+      </c>
+      <c r="Y180" s="3">
+        <v>6064.0</v>
+      </c>
+      <c r="AA180" s="3">
+        <v>5178.0</v>
+      </c>
+      <c r="AB180" s="3">
+        <v>64004.399999999994</v>
+      </c>
+      <c r="AC180" s="3">
+        <v>-0.19999999999708962</v>
+      </c>
+      <c r="AD180" s="3">
+        <v>0.2657536135519716</v>
+      </c>
+      <c r="AE180" s="3">
+        <v>2000.0</v>
+      </c>
+      <c r="AH180" s="3">
+        <v>135.0</v>
+      </c>
+      <c r="AI180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ180" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK180" s="3">
+        <v>844.0</v>
+      </c>
+      <c r="AL180" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AM180" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="AN180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO180" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AP180" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="AQ180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS180" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="AT180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU180" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="AV180" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J186" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M186" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="N186" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O186" s="3">
+        <v>675.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M187" s="3">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P188" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="Q188" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R188" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S188" s="3">
+        <v>10760.8</v>
+      </c>
+      <c r="T188" s="3">
+        <v>9424.0</v>
+      </c>
+      <c r="U188" s="3">
+        <v>13910.0</v>
+      </c>
+      <c r="V188" s="3">
+        <v>12303.0</v>
+      </c>
+      <c r="W188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X188" s="3">
+        <v>776.0</v>
+      </c>
+      <c r="Y188" s="3">
+        <v>3652.0</v>
+      </c>
+      <c r="AA188" s="3">
+        <v>3265.0</v>
+      </c>
+      <c r="AB188" s="3">
+        <v>54989.3</v>
+      </c>
+      <c r="AC188" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD188" s="3">
+        <v>0.3535972612712983</v>
+      </c>
+      <c r="AE188" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AI188" s="3">
+        <v>675.0</v>
+      </c>
+      <c r="AJ188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM188" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AN188" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO188" s="3">
+        <v>136.0</v>
+      </c>
+      <c r="AP188" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="AQ188" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU188" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV188" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -6172,7 +8108,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -6192,7 +8128,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>106</v>
@@ -6212,7 +8148,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>106</v>
@@ -6232,7 +8168,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
@@ -6255,7 +8191,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>106</v>
@@ -6278,7 +8214,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>106</v>
@@ -6341,7 +8277,7 @@
         <v>3.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AN7" s="3">
         <v>0.0</v>
@@ -6373,7 +8309,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>112</v>
@@ -6393,7 +8329,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>112</v>
@@ -6413,7 +8349,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>112</v>
@@ -6436,7 +8372,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>112</v>
@@ -6496,7 +8432,7 @@
         <v>4.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
@@ -6528,7 +8464,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -6548,7 +8484,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -6568,7 +8504,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -6591,7 +8527,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -6614,7 +8550,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -6637,7 +8573,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -6700,7 +8636,7 @@
         <v>2.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="AN17" s="3">
         <v>0.0</v>
@@ -6732,7 +8668,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>73</v>
@@ -6752,7 +8688,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>73</v>
@@ -6772,7 +8708,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>73</v>
@@ -6784,10 +8720,10 @@
         <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>89</v>
@@ -6795,7 +8731,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>73</v>
@@ -6824,7 +8760,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>73</v>
@@ -6847,7 +8783,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>73</v>
@@ -6907,7 +8843,7 @@
         <v>0.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AN23" s="3">
         <v>1.0</v>
@@ -6939,7 +8875,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>83</v>
@@ -6959,7 +8895,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>83</v>
@@ -6979,7 +8915,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>83</v>
@@ -7002,7 +8938,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>83</v>
@@ -7031,7 +8967,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>83</v>
@@ -7094,7 +9030,7 @@
         <v>0.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -7126,7 +9062,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>92</v>
@@ -7146,7 +9082,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
@@ -7166,7 +9102,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
@@ -7189,7 +9125,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -7218,7 +9154,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
@@ -7281,7 +9217,7 @@
         <v>3.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="AN33" s="3">
         <v>1.0</v>
@@ -7313,7 +9249,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>98</v>
@@ -7333,7 +9269,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>98</v>
@@ -7353,7 +9289,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>98</v>
@@ -7373,7 +9309,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>98</v>
@@ -7402,7 +9338,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>98</v>
@@ -7425,7 +9361,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -7494,7 +9430,7 @@
         <v>1.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -7526,7 +9462,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>106</v>
@@ -7546,7 +9482,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>106</v>
@@ -7566,7 +9502,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>106</v>
@@ -7589,7 +9525,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>106</v>
@@ -7612,7 +9548,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -7675,7 +9611,7 @@
         <v>2.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="AN44" s="3">
         <v>0.0</v>
@@ -7707,7 +9643,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>112</v>
@@ -7727,7 +9663,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>112</v>
@@ -7747,7 +9683,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>112</v>
@@ -7770,7 +9706,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>112</v>
@@ -7833,7 +9769,7 @@
         <v>2.0</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="AN48" s="3">
         <v>0.0</v>
@@ -7865,7 +9801,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -7885,7 +9821,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -7905,7 +9841,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -7925,7 +9861,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -7948,7 +9884,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -7977,7 +9913,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -8000,7 +9936,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -8063,7 +9999,7 @@
         <v>0.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -8095,7 +10031,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>73</v>
@@ -8115,7 +10051,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>73</v>
@@ -8135,7 +10071,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>73</v>
@@ -8155,7 +10091,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>73</v>
@@ -8175,7 +10111,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>73</v>
@@ -8202,7 +10138,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>73</v>
@@ -8235,7 +10171,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>73</v>
@@ -8293,7 +10229,7 @@
         <v>2.0</v>
       </c>
       <c r="AM62" s="1" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="AN62" s="3">
         <v>1.0</v>
@@ -8325,7 +10261,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>83</v>
@@ -8345,7 +10281,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>83</v>
@@ -8365,7 +10301,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>83</v>
@@ -8388,7 +10324,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>83</v>
@@ -8454,7 +10390,7 @@
         <v>2.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="AN66" s="3">
         <v>0.0</v>
@@ -8486,7 +10422,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>92</v>
@@ -8506,7 +10442,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>92</v>
@@ -8526,7 +10462,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>92</v>
@@ -8546,7 +10482,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>92</v>
@@ -8569,7 +10505,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>92</v>
@@ -8598,7 +10534,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>92</v>
@@ -8610,7 +10546,7 @@
         <v>99</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>102</v>
@@ -8618,7 +10554,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>92</v>
@@ -8678,7 +10614,7 @@
         <v>3.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="AN73" s="3">
         <v>1.0</v>
@@ -8710,7 +10646,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>98</v>
@@ -8730,7 +10666,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>98</v>
@@ -8750,7 +10686,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>98</v>
@@ -8770,7 +10706,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>98</v>
@@ -8799,7 +10735,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>98</v>
@@ -8822,7 +10758,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>98</v>
@@ -8885,7 +10821,7 @@
         <v>3.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -8917,7 +10853,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>106</v>
@@ -8937,7 +10873,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>106</v>
@@ -8957,7 +10893,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>106</v>
@@ -8977,7 +10913,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>106</v>
@@ -9000,7 +10936,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>106</v>
@@ -9023,7 +10959,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>106</v>
@@ -9092,7 +11028,7 @@
         <v>4.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="AN85" s="3">
         <v>0.0</v>
@@ -9124,7 +11060,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>112</v>
@@ -9144,7 +11080,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>112</v>
@@ -9164,7 +11100,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>112</v>
@@ -9184,7 +11120,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>112</v>
@@ -9213,7 +11149,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>112</v>
@@ -9236,7 +11172,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>112</v>
@@ -9299,7 +11235,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -9331,7 +11267,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
@@ -9351,7 +11287,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -9371,7 +11307,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -9391,7 +11327,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>49</v>
@@ -9420,7 +11356,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -9443,7 +11379,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -9466,7 +11402,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -9529,7 +11465,7 @@
         <v>1.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AN98" s="3">
         <v>1.0</v>
@@ -9561,7 +11497,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>73</v>
@@ -9581,7 +11517,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>73</v>
@@ -9601,7 +11537,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>73</v>
@@ -9621,7 +11557,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>73</v>
@@ -9641,7 +11577,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>73</v>
@@ -9661,7 +11597,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>73</v>
@@ -9688,7 +11624,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>73</v>
@@ -9701,7 +11637,7 @@
         <v>80</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>93</v>
@@ -9715,7 +11651,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>73</v>
@@ -9785,7 +11721,7 @@
         <v>1.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="AN106" s="3">
         <v>0.0</v>
@@ -9817,7 +11753,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>83</v>
@@ -9837,7 +11773,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>83</v>
@@ -9857,7 +11793,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>83</v>
@@ -9877,7 +11813,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>83</v>
@@ -9900,7 +11836,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>83</v>
@@ -9923,7 +11859,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>83</v>
@@ -9989,7 +11925,7 @@
         <v>2.0</v>
       </c>
       <c r="AM112" s="1" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="AN112" s="3">
         <v>0.0</v>
@@ -10021,7 +11957,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>92</v>
@@ -10041,7 +11977,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>92</v>
@@ -10061,7 +11997,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>92</v>
@@ -10081,7 +12017,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>92</v>
@@ -10104,7 +12040,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>92</v>
@@ -10164,7 +12100,7 @@
         <v>2.0</v>
       </c>
       <c r="AM117" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="AN117" s="3">
         <v>0.0</v>
@@ -10196,7 +12132,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>98</v>
@@ -10216,7 +12152,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>98</v>
@@ -10236,7 +12172,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>98</v>
@@ -10256,7 +12192,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>98</v>
@@ -10285,7 +12221,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>98</v>
@@ -10308,7 +12244,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>98</v>
@@ -10368,7 +12304,7 @@
         <v>2.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -10400,7 +12336,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>106</v>
@@ -10420,7 +12356,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>106</v>
@@ -10440,7 +12376,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>106</v>
@@ -10460,7 +12396,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>106</v>
@@ -10483,7 +12419,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>106</v>
@@ -10506,7 +12442,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>106</v>
@@ -10569,7 +12505,7 @@
         <v>0.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="AN129" s="3">
         <v>0.0</v>
@@ -10601,7 +12537,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>112</v>
@@ -10621,7 +12557,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>112</v>
@@ -10641,7 +12577,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>112</v>
@@ -10661,7 +12597,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>112</v>
@@ -10684,7 +12620,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>112</v>
@@ -10707,7 +12643,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>112</v>
@@ -10767,7 +12703,7 @@
         <v>0.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="AN135" s="3">
         <v>0.0</v>
@@ -10799,7 +12735,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>49</v>
@@ -10819,7 +12755,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>49</v>
@@ -10839,7 +12775,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>49</v>
@@ -10859,7 +12795,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -10888,7 +12824,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
@@ -10911,7 +12847,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -10968,7 +12904,7 @@
         <v>2.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="AN141" s="3">
         <v>1.0</v>
@@ -11000,7 +12936,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>73</v>
@@ -11020,7 +12956,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>73</v>
@@ -11040,7 +12976,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>73</v>
@@ -11060,7 +12996,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>73</v>
@@ -11080,7 +13016,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>73</v>
@@ -11109,7 +13045,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>73</v>
@@ -11201,7 +13137,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>83</v>
@@ -11221,7 +13157,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>83</v>
@@ -11241,7 +13177,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>83</v>
@@ -11261,7 +13197,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>83</v>
@@ -11281,7 +13217,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>83</v>
@@ -11310,7 +13246,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>83</v>
@@ -11333,7 +13269,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>83</v>
@@ -11399,7 +13335,7 @@
         <v>0.0</v>
       </c>
       <c r="AM154" s="1" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="AN154" s="3">
         <v>1.0</v>
@@ -11431,7 +13367,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>92</v>
@@ -11451,7 +13387,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>92</v>
@@ -11471,7 +13407,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>92</v>
@@ -11494,7 +13430,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>92</v>
@@ -11548,7 +13484,7 @@
         <v>1.0</v>
       </c>
       <c r="AM158" s="1" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="AN158" s="3">
         <v>0.0</v>
@@ -11580,7 +13516,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>98</v>
@@ -11600,7 +13536,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>98</v>
@@ -11620,7 +13556,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>98</v>
@@ -11643,7 +13579,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>98</v>
@@ -11672,7 +13608,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>98</v>
@@ -11732,7 +13668,7 @@
         <v>3.0</v>
       </c>
       <c r="AM163" s="1" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AN163" s="3">
         <v>1.0</v>
@@ -11764,7 +13700,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>106</v>
@@ -11784,7 +13720,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>106</v>
@@ -11804,7 +13740,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>106</v>
@@ -11824,7 +13760,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>106</v>
@@ -11847,7 +13783,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>106</v>
@@ -11876,7 +13812,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>106</v>
@@ -11939,7 +13875,7 @@
         <v>1.0</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="AN169" s="3">
         <v>1.0</v>
@@ -11971,7 +13907,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>112</v>
@@ -11991,7 +13927,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>112</v>
@@ -12011,7 +13947,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>112</v>
@@ -12031,7 +13967,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>112</v>
@@ -12051,7 +13987,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>112</v>
@@ -12074,7 +14010,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>112</v>
@@ -12097,7 +14033,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>112</v>
@@ -12160,7 +14096,7 @@
         <v>2.0</v>
       </c>
       <c r="AM176" s="1" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="AN176" s="3">
         <v>0.0</v>
@@ -12350,7 +14286,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>83</v>
@@ -12370,7 +14306,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>83</v>
@@ -12390,7 +14326,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>83</v>
@@ -12410,7 +14346,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>83</v>
@@ -12439,7 +14375,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>83</v>
@@ -12462,7 +14398,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>83</v>
@@ -12557,7 +14493,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>92</v>
@@ -12577,7 +14513,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>92</v>
@@ -12597,7 +14533,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>92</v>
@@ -12620,7 +14556,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>92</v>
@@ -12649,13 +14585,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>51</v>
@@ -12678,7 +14614,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>92</v>
@@ -12741,7 +14677,7 @@
         <v>2.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -12773,7 +14709,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>98</v>
@@ -12793,7 +14729,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>98</v>
@@ -12813,13 +14749,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>51</v>
@@ -12842,7 +14778,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>98</v>
@@ -12865,7 +14801,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>98</v>
@@ -12925,7 +14861,7 @@
         <v>1.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="AN18" s="3">
         <v>1.0</v>
@@ -12957,7 +14893,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>106</v>
@@ -12977,7 +14913,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>106</v>
@@ -12997,7 +14933,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>106</v>
@@ -13017,7 +14953,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>106</v>
@@ -13040,7 +14976,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>106</v>
@@ -13097,7 +15033,7 @@
         <v>1.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="AN23" s="3">
         <v>0.0</v>
@@ -13129,7 +15065,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>112</v>
@@ -13149,7 +15085,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>112</v>
@@ -13169,7 +15105,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>112</v>
@@ -13198,7 +15134,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>112</v>
@@ -13221,7 +15157,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>112</v>
@@ -13281,7 +15217,7 @@
         <v>0.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -13313,7 +15249,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>49</v>
@@ -13333,7 +15269,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -13353,7 +15289,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -13373,7 +15309,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
@@ -13402,7 +15338,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -13425,7 +15361,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -13488,7 +15424,7 @@
         <v>3.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="AN34" s="3">
         <v>1.0</v>
@@ -13520,7 +15456,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>73</v>
@@ -13540,7 +15476,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>73</v>
@@ -13560,7 +15496,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>73</v>
@@ -13580,7 +15516,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>73</v>
@@ -13603,7 +15539,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>73</v>
@@ -13632,7 +15568,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>73</v>
@@ -13655,7 +15591,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>73</v>
@@ -13712,7 +15648,7 @@
         <v>1.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -13744,7 +15680,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>83</v>
@@ -13764,7 +15700,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>83</v>
@@ -13784,7 +15720,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>83</v>
@@ -13804,7 +15740,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>83</v>
@@ -13827,7 +15763,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>83</v>
@@ -13850,7 +15786,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>83</v>
@@ -13913,7 +15849,7 @@
         <v>3.0</v>
       </c>
       <c r="AM47" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="AN47" s="3">
         <v>0.0</v>
@@ -13945,7 +15881,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>92</v>
@@ -13965,7 +15901,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>92</v>
@@ -13985,7 +15921,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>92</v>
@@ -13997,7 +15933,7 @@
         <v>61</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>59</v>
@@ -14008,7 +15944,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>92</v>
@@ -14017,7 +15953,7 @@
         <v>63</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>148</v>
@@ -14037,13 +15973,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>51</v>
@@ -14066,7 +16002,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>92</v>
@@ -14126,7 +16062,7 @@
         <v>1.0</v>
       </c>
       <c r="AM53" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AN53" s="3">
         <v>2.0</v>
@@ -14158,7 +16094,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>98</v>
@@ -14178,7 +16114,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>98</v>
@@ -14198,7 +16134,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>98</v>
@@ -14218,7 +16154,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>98</v>
@@ -14247,7 +16183,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>98</v>
@@ -14270,7 +16206,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>98</v>
@@ -14330,7 +16266,7 @@
         <v>2.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="AN59" s="3">
         <v>1.0</v>
@@ -14362,7 +16298,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>106</v>
@@ -14382,7 +16318,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>106</v>
@@ -14402,7 +16338,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>106</v>
@@ -14411,7 +16347,7 @@
         <v>108</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>79</v>
@@ -14422,7 +16358,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>106</v>
@@ -14445,7 +16381,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>106</v>
@@ -14468,7 +16404,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>106</v>
@@ -14531,7 +16467,7 @@
         <v>0.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AN65" s="3">
         <v>0.0</v>
@@ -14563,7 +16499,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>112</v>
@@ -14583,7 +16519,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>112</v>
@@ -14603,7 +16539,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>112</v>
@@ -14623,7 +16559,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>112</v>
@@ -14646,7 +16582,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>112</v>
@@ -14703,7 +16639,7 @@
         <v>2.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="AN70" s="3">
         <v>0.0</v>
@@ -14735,7 +16671,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
@@ -14755,7 +16691,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -14775,7 +16711,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -14795,7 +16731,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
@@ -14824,7 +16760,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -14847,7 +16783,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
@@ -14904,7 +16840,7 @@
         <v>2.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -14936,7 +16872,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>73</v>
@@ -14956,7 +16892,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>73</v>
@@ -14976,7 +16912,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>73</v>
@@ -14996,7 +16932,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>73</v>
@@ -15019,7 +16955,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>73</v>
@@ -15042,7 +16978,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>73</v>
@@ -15105,7 +17041,7 @@
         <v>1.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="AN82" s="3">
         <v>0.0</v>
@@ -15137,7 +17073,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>83</v>
@@ -15157,7 +17093,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>83</v>
@@ -15177,7 +17113,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>83</v>
@@ -15197,7 +17133,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>83</v>
@@ -15220,7 +17156,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>83</v>
@@ -15243,7 +17179,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>83</v>
@@ -15306,7 +17242,7 @@
         <v>0.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="AN88" s="3">
         <v>0.0</v>
@@ -15338,7 +17274,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>92</v>
@@ -15358,7 +17294,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>92</v>
@@ -15378,7 +17314,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>92</v>
@@ -15401,7 +17337,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>92</v>
@@ -15458,7 +17394,7 @@
         <v>1.0</v>
       </c>
       <c r="AM92" s="1" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="AN92" s="3">
         <v>0.0</v>
@@ -15490,7 +17426,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>98</v>
@@ -15510,7 +17446,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>98</v>
@@ -15530,7 +17466,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>98</v>
@@ -15553,7 +17489,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>98</v>
@@ -15576,7 +17512,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>98</v>
@@ -15639,7 +17575,7 @@
         <v>1.0</v>
       </c>
       <c r="AM97" s="1" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="AN97" s="3">
         <v>0.0</v>
@@ -15671,7 +17607,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>106</v>
@@ -15691,7 +17627,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
@@ -15711,7 +17647,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -15740,7 +17676,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>106</v>
@@ -15763,7 +17699,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>106</v>
@@ -15826,7 +17762,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AN102" s="3">
         <v>1.0</v>
@@ -15858,7 +17794,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>112</v>
@@ -15878,7 +17814,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>112</v>
@@ -15898,7 +17834,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>112</v>
@@ -15918,7 +17854,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
@@ -15941,7 +17877,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>112</v>
@@ -15964,7 +17900,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>112</v>
@@ -16024,7 +17960,7 @@
         <v>2.0</v>
       </c>
       <c r="AM108" s="1" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AN108" s="3">
         <v>0.0</v>
@@ -16056,7 +17992,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>49</v>
@@ -16076,7 +18012,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -16085,7 +18021,7 @@
         <v>75</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>64</v>
@@ -16096,7 +18032,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
@@ -16116,7 +18052,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -16139,7 +18075,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
@@ -16162,7 +18098,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -16225,7 +18161,7 @@
         <v>5.0</v>
       </c>
       <c r="AM114" s="1" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="AN114" s="3">
         <v>0.0</v>
@@ -16257,7 +18193,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>73</v>
@@ -16277,7 +18213,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>73</v>
@@ -16297,7 +18233,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>73</v>
@@ -16317,7 +18253,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>73</v>
@@ -16337,7 +18273,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>73</v>
@@ -16364,7 +18300,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>73</v>
@@ -16391,7 +18327,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>73</v>
@@ -16461,7 +18397,7 @@
         <v>2.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="AN121" s="3">
         <v>0.0</v>
@@ -16493,7 +18429,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>83</v>
@@ -16513,7 +18449,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>83</v>
@@ -16533,7 +18469,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>83</v>
@@ -16553,7 +18489,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>83</v>
@@ -16573,7 +18509,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>83</v>
@@ -16602,7 +18538,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>83</v>
@@ -16625,7 +18561,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>83</v>
@@ -16688,7 +18624,7 @@
         <v>1.0</v>
       </c>
       <c r="AM128" s="1" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AN128" s="3">
         <v>1.0</v>
@@ -16720,7 +18656,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>92</v>
@@ -16740,7 +18676,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>92</v>
@@ -16760,7 +18696,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>92</v>
@@ -16783,7 +18719,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>92</v>
@@ -16812,7 +18748,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>92</v>
@@ -16869,7 +18805,7 @@
         <v>0.0</v>
       </c>
       <c r="AM133" s="1" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="AN133" s="3">
         <v>1.0</v>
@@ -16901,7 +18837,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>98</v>
@@ -16921,7 +18857,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>98</v>
@@ -16941,7 +18877,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>98</v>
@@ -16961,7 +18897,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>98</v>
@@ -16984,7 +18920,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>98</v>
@@ -17013,7 +18949,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>98</v>
@@ -17073,7 +19009,7 @@
         <v>1.0</v>
       </c>
       <c r="AM139" s="1" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AN139" s="3">
         <v>1.0</v>
@@ -17105,7 +19041,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>106</v>
@@ -17125,7 +19061,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>106</v>
@@ -17145,7 +19081,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>106</v>
@@ -17168,7 +19104,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>106</v>
@@ -17191,7 +19127,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>106</v>
@@ -17248,7 +19184,7 @@
         <v>1.0</v>
       </c>
       <c r="AM144" s="1" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="AN144" s="3">
         <v>0.0</v>
@@ -17280,7 +19216,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>112</v>
@@ -17300,7 +19236,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>112</v>
@@ -17320,7 +19256,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>112</v>
@@ -17340,7 +19276,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>112</v>
@@ -17363,7 +19299,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>112</v>
@@ -17386,7 +19322,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>112</v>
@@ -17446,7 +19382,7 @@
         <v>1.0</v>
       </c>
       <c r="AM150" s="1" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AN150" s="3">
         <v>0.0</v>
@@ -17478,7 +19414,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -17498,7 +19434,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
@@ -17518,7 +19454,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -17538,7 +19474,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -17547,7 +19483,7 @@
         <v>63</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>79</v>
@@ -17567,7 +19503,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -17590,7 +19526,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -17688,7 +19624,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>73</v>
@@ -17700,7 +19636,7 @@
         <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>117</v>
@@ -17708,7 +19644,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>73</v>
@@ -17728,7 +19664,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>73</v>
@@ -17748,7 +19684,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>73</v>
@@ -17771,7 +19707,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>73</v>
@@ -17794,7 +19730,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>73</v>
@@ -17857,7 +19793,7 @@
         <v>0.0</v>
       </c>
       <c r="AM162" s="1" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="AN162" s="3">
         <v>0.0</v>
@@ -17889,7 +19825,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>83</v>
@@ -17909,7 +19845,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>83</v>
@@ -17929,7 +19865,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>83</v>
@@ -17952,7 +19888,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>83</v>
@@ -17975,7 +19911,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>83</v>
@@ -18038,7 +19974,7 @@
         <v>1.0</v>
       </c>
       <c r="AM167" s="1" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="AN167" s="3">
         <v>0.0</v>
@@ -18070,7 +20006,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>92</v>
@@ -18090,7 +20026,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>92</v>
@@ -18110,7 +20046,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>92</v>
@@ -18133,7 +20069,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>92</v>
@@ -18162,7 +20098,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>92</v>
@@ -18225,7 +20161,7 @@
         <v>0.0</v>
       </c>
       <c r="AM172" s="1" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="AN172" s="3">
         <v>1.0</v>
@@ -18257,7 +20193,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>98</v>
@@ -18269,7 +20205,7 @@
         <v>53</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>117</v>
@@ -18277,7 +20213,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>98</v>
@@ -18297,7 +20233,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>98</v>
@@ -18317,7 +20253,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>98</v>
@@ -18340,7 +20276,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>98</v>
@@ -18369,7 +20305,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>98</v>
@@ -18429,7 +20365,7 @@
         <v>0.0</v>
       </c>
       <c r="AM178" s="1" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="AN178" s="3">
         <v>1.0</v>
@@ -18630,7 +20566,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>83</v>
@@ -18650,7 +20586,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>83</v>
@@ -18670,7 +20606,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>83</v>
@@ -18690,7 +20626,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>83</v>
@@ -18713,7 +20649,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>83</v>
@@ -18742,7 +20678,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>83</v>
@@ -18808,7 +20744,7 @@
         <v>1.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="AN7" s="3">
         <v>1.0</v>
@@ -18840,7 +20776,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>92</v>
@@ -18860,13 +20796,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>61</v>
@@ -18889,7 +20825,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>92</v>
@@ -18909,7 +20845,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>92</v>
@@ -18932,7 +20868,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>92</v>
@@ -18986,7 +20922,7 @@
         <v>1.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="AN12" s="3">
         <v>1.0</v>
@@ -19018,7 +20954,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>98</v>
@@ -19038,7 +20974,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>98</v>
@@ -19061,13 +20997,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>51</v>
@@ -19090,7 +21026,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>98</v>
@@ -19144,7 +21080,7 @@
         <v>4.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="AN16" s="3">
         <v>1.0</v>
@@ -19176,7 +21112,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>106</v>
@@ -19196,7 +21132,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>106</v>
@@ -19219,7 +21155,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>106</v>
@@ -19239,7 +21175,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>106</v>
@@ -19262,7 +21198,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>106</v>
@@ -19325,7 +21261,7 @@
         <v>1.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="AN21" s="3">
         <v>0.0</v>
@@ -19357,7 +21293,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>112</v>
@@ -19377,7 +21313,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>112</v>
@@ -19397,7 +21333,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>112</v>
@@ -19417,7 +21353,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>112</v>
@@ -19440,7 +21376,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>112</v>
@@ -19506,7 +21442,7 @@
         <v>4.0</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="AN26" s="3">
         <v>0.0</v>
@@ -19538,7 +21474,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>49</v>
@@ -19558,7 +21494,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>49</v>
@@ -19578,7 +21514,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>49</v>
@@ -19598,7 +21534,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -19618,7 +21554,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -19645,7 +21581,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
@@ -19672,7 +21608,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -19733,7 +21669,7 @@
         <v>4.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="AN33" s="3">
         <v>0.0</v>
@@ -19765,7 +21701,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>73</v>
@@ -19785,7 +21721,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>73</v>
@@ -19805,7 +21741,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>73</v>
@@ -19825,7 +21761,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>73</v>
@@ -19845,13 +21781,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>51</v>
@@ -19874,7 +21810,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>73</v>
@@ -19897,7 +21833,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>73</v>
@@ -19957,7 +21893,7 @@
         <v>5.0</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="AN40" s="3">
         <v>1.0</v>
@@ -19989,7 +21925,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>83</v>
@@ -20009,7 +21945,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>83</v>
@@ -20029,7 +21965,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>83</v>
@@ -20052,7 +21988,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>83</v>
@@ -20075,7 +22011,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>83</v>
@@ -20164,7 +22100,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>92</v>
@@ -20184,7 +22120,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
@@ -20204,7 +22140,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>92</v>
@@ -20227,7 +22163,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>92</v>
@@ -20256,7 +22192,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>92</v>
@@ -20313,7 +22249,7 @@
         <v>3.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="AN50" s="3">
         <v>1.0</v>
@@ -20345,7 +22281,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>98</v>
@@ -20365,7 +22301,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>98</v>
@@ -20385,7 +22321,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>98</v>
@@ -20408,7 +22344,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>98</v>
@@ -20431,7 +22367,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>98</v>
@@ -20497,7 +22433,7 @@
         <v>7.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="AN55" s="3">
         <v>0.0</v>
@@ -20529,7 +22465,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>106</v>
@@ -20549,7 +22485,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>106</v>
@@ -20569,7 +22505,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>106</v>
@@ -20592,7 +22528,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>106</v>
@@ -20615,7 +22551,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>106</v>
@@ -20681,7 +22617,7 @@
         <v>0.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>298</v>
+        <v>167</v>
       </c>
       <c r="AN60" s="3">
         <v>0.0</v>
@@ -20713,7 +22649,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>112</v>
@@ -20733,7 +22669,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>112</v>
@@ -20753,7 +22689,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>112</v>
@@ -20776,13 +22712,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>51</v>
@@ -20805,7 +22741,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>112</v>
@@ -20862,7 +22798,7 @@
         <v>0.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -20894,7 +22830,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -20914,7 +22850,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -20934,13 +22870,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>51</v>
@@ -20954,7 +22890,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
@@ -20983,7 +22919,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -21006,7 +22942,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
@@ -21029,7 +22965,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -21092,7 +23028,7 @@
         <v>10.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="AN72" s="3">
         <v>1.0</v>
@@ -21124,7 +23060,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>73</v>
@@ -21144,7 +23080,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>73</v>
@@ -21164,7 +23100,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>73</v>
@@ -21184,7 +23120,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>73</v>
@@ -21211,7 +23147,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>73</v>
@@ -21221,7 +23157,7 @@
       <c r="E77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>130</v>
@@ -21244,7 +23180,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>73</v>
@@ -21311,7 +23247,7 @@
         <v>3.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -21343,7 +23279,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>83</v>
@@ -21363,7 +23299,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>83</v>
@@ -21383,7 +23319,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>83</v>
@@ -21403,7 +23339,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>83</v>
@@ -21426,7 +23362,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>83</v>
@@ -21449,7 +23385,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>83</v>
@@ -21478,7 +23414,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>83</v>
@@ -21541,7 +23477,7 @@
         <v>2.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="AN85" s="3">
         <v>1.0</v>
@@ -21573,7 +23509,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>92</v>
@@ -21593,7 +23529,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>92</v>
@@ -21613,7 +23549,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>92</v>
@@ -21636,13 +23572,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>89</v>
@@ -21665,7 +23601,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>92</v>
@@ -21728,7 +23664,7 @@
         <v>2.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -21760,7 +23696,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>98</v>
@@ -21780,7 +23716,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>98</v>
@@ -21800,7 +23736,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>98</v>
@@ -21823,7 +23759,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>98</v>
@@ -21852,7 +23788,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>98</v>
@@ -21944,7 +23880,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>106</v>
@@ -21956,7 +23892,7 @@
         <v>53</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>128</v>
@@ -21964,7 +23900,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>106</v>
@@ -21984,7 +23920,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>106</v>
@@ -22004,7 +23940,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
@@ -22027,7 +23963,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
@@ -22050,7 +23986,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>106</v>
@@ -22110,7 +24046,7 @@
         <v>2.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="AN101" s="3">
         <v>0.0</v>
@@ -22142,7 +24078,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>112</v>
@@ -22162,7 +24098,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>112</v>
@@ -22182,7 +24118,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>112</v>
@@ -22202,7 +24138,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>112</v>
@@ -22225,13 +24161,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>51</v>
@@ -22254,7 +24190,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>112</v>
@@ -22317,7 +24253,7 @@
         <v>2.0</v>
       </c>
       <c r="AM107" s="1" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="AN107" s="3">
         <v>1.0</v>
@@ -22349,7 +24285,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>49</v>
@@ -22369,7 +24305,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>49</v>
@@ -22389,7 +24325,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -22412,7 +24348,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
@@ -22435,13 +24371,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -22464,7 +24400,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
@@ -22524,7 +24460,7 @@
         <v>1.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="AN113" s="3">
         <v>1.0</v>
@@ -22556,7 +24492,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>73</v>
@@ -22576,7 +24512,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>73</v>
@@ -22596,7 +24532,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>73</v>
@@ -22616,7 +24552,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>73</v>
@@ -22639,7 +24575,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>73</v>
@@ -22662,7 +24598,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>73</v>
@@ -22728,7 +24664,7 @@
         <v>6.0</v>
       </c>
       <c r="AM119" s="1" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AN119" s="3">
         <v>0.0</v>
@@ -22760,7 +24696,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>83</v>
@@ -22780,7 +24716,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>83</v>
@@ -22800,7 +24736,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>83</v>
@@ -22820,13 +24756,13 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>83</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>51</v>
@@ -22849,7 +24785,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>83</v>
@@ -22872,7 +24808,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>83</v>
@@ -22967,7 +24903,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>92</v>
@@ -22987,7 +24923,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>92</v>
@@ -22999,7 +24935,7 @@
         <v>66</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>70</v>
@@ -23007,7 +24943,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>92</v>
@@ -23030,7 +24966,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>92</v>
@@ -23059,7 +24995,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>92</v>
@@ -23122,7 +25058,7 @@
         <v>1.0</v>
       </c>
       <c r="AM130" s="1" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="AN130" s="3">
         <v>1.0</v>
@@ -23154,7 +25090,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>98</v>
@@ -23174,7 +25110,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>98</v>
@@ -23194,7 +25130,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>98</v>
@@ -23206,7 +25142,7 @@
         <v>130</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>122</v>
@@ -23214,7 +25150,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>98</v>
@@ -23243,13 +25179,13 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>51</v>
@@ -23272,7 +25208,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>98</v>
@@ -23332,7 +25268,7 @@
         <v>1.0</v>
       </c>
       <c r="AM136" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="AN136" s="3">
         <v>2.0</v>
@@ -23364,7 +25300,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>106</v>
@@ -23384,7 +25320,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>106</v>
@@ -23404,7 +25340,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>106</v>
@@ -23427,7 +25363,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>106</v>
@@ -23450,7 +25386,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>106</v>
@@ -23513,7 +25449,7 @@
         <v>0.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="AN141" s="3">
         <v>0.0</v>
@@ -23545,7 +25481,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>112</v>
@@ -23565,7 +25501,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>112</v>
@@ -23585,7 +25521,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>112</v>
@@ -23597,7 +25533,7 @@
         <v>51</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>70</v>
@@ -23605,7 +25541,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>112</v>
@@ -23628,7 +25564,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>112</v>
@@ -23651,7 +25587,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>112</v>
@@ -23711,7 +25647,7 @@
         <v>1.0</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="AN147" s="3">
         <v>0.0</v>
@@ -23743,7 +25679,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>49</v>
@@ -23763,7 +25699,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>49</v>
@@ -23783,7 +25719,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>49</v>
@@ -23795,7 +25731,7 @@
         <v>88</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>132</v>
@@ -23803,7 +25739,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -23826,13 +25762,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>51</v>
@@ -23855,7 +25791,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -23878,7 +25814,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -23941,7 +25877,7 @@
         <v>2.0</v>
       </c>
       <c r="AM154" s="1" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="AN154" s="3">
         <v>1.0</v>
@@ -23973,7 +25909,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>73</v>
@@ -23993,7 +25929,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>73</v>
@@ -24013,13 +25949,13 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>51</v>
@@ -24042,7 +25978,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>73</v>
@@ -24065,7 +26001,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>73</v>
@@ -24085,7 +26021,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>73</v>
@@ -24338,7 +26274,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>112</v>
@@ -24358,7 +26294,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>112</v>
@@ -24378,7 +26314,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>112</v>
@@ -24398,7 +26334,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>112</v>
@@ -24418,7 +26354,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>112</v>
@@ -24441,7 +26377,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>112</v>
@@ -24464,7 +26400,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>112</v>
@@ -24527,7 +26463,7 @@
         <v>5.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="AN8" s="3">
         <v>0.0</v>
@@ -24559,7 +26495,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -24579,13 +26515,13 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>51</v>
@@ -24599,7 +26535,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -24619,7 +26555,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -24642,7 +26578,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -24665,7 +26601,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -24688,7 +26624,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -24700,7 +26636,7 @@
         <v>50</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="S15" s="3">
         <v>16534.0</v>
@@ -24751,7 +26687,7 @@
         <v>3.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="AN15" s="3">
         <v>0.0</v>
@@ -24783,7 +26719,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>73</v>
@@ -24803,7 +26739,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>73</v>
@@ -24823,7 +26759,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>73</v>
@@ -24843,7 +26779,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>73</v>
@@ -24863,7 +26799,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>73</v>
@@ -24886,7 +26822,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>73</v>
@@ -24909,7 +26845,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>73</v>
@@ -24975,7 +26911,7 @@
         <v>4.0</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="AN22" s="3">
         <v>0.0</v>
@@ -25007,7 +26943,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>83</v>
@@ -25027,13 +26963,13 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>53</v>
@@ -25047,7 +26983,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>83</v>
@@ -25067,7 +27003,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>83</v>
@@ -25090,7 +27026,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>83</v>
@@ -25119,7 +27055,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>83</v>
@@ -25128,7 +27064,7 @@
         <v>8.0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>75</v>
@@ -25179,7 +27115,7 @@
         <v>6.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -25211,7 +27147,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>92</v>
@@ -25231,7 +27167,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>92</v>
@@ -25251,7 +27187,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>92</v>
@@ -25271,7 +27207,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>92</v>
@@ -25294,13 +27230,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>51</v>
@@ -25323,7 +27259,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>92</v>
@@ -25380,7 +27316,7 @@
         <v>3.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="AN34" s="3">
         <v>1.0</v>
@@ -25412,7 +27348,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>98</v>
@@ -25432,7 +27368,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>98</v>
@@ -25452,7 +27388,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>98</v>
@@ -25472,13 +27408,13 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>51</v>
@@ -25492,7 +27428,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -25515,13 +27451,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>51</v>
@@ -25544,7 +27480,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>98</v>
@@ -25607,7 +27543,7 @@
         <v>3.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>338</v>
+        <v>165</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -25639,7 +27575,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>106</v>
@@ -25659,13 +27595,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>53</v>
@@ -25679,7 +27615,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -25702,7 +27638,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>106</v>
@@ -25714,7 +27650,7 @@
         <v>51</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>70</v>
@@ -25731,7 +27667,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>106</v>
@@ -25791,7 +27727,7 @@
         <v>3.0</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="AN46" s="3">
         <v>1.0</v>
@@ -25823,7 +27759,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>112</v>
@@ -25843,7 +27779,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>112</v>
@@ -25863,7 +27799,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>112</v>
@@ -25886,13 +27822,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>51</v>
@@ -25915,7 +27851,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>112</v>
@@ -25944,7 +27880,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>112</v>
@@ -26007,7 +27943,7 @@
         <v>12.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="AN52" s="3">
         <v>2.0</v>
@@ -26039,7 +27975,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -26059,7 +27995,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -26079,7 +28015,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -26102,7 +28038,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>49</v>
@@ -26125,13 +28061,13 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>51</v>
@@ -26154,7 +28090,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>49</v>
@@ -26220,7 +28156,7 @@
         <v>9.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="AN58" s="3">
         <v>1.0</v>
@@ -26252,7 +28188,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>73</v>
@@ -26272,7 +28208,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>73</v>
@@ -26292,7 +28228,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>73</v>
@@ -26312,7 +28248,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>73</v>
@@ -26332,7 +28268,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>73</v>
@@ -26355,7 +28291,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>73</v>
@@ -26384,7 +28320,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>73</v>
@@ -26447,7 +28383,7 @@
         <v>6.0</v>
       </c>
       <c r="AM65" s="1" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="AN65" s="3">
         <v>1.0</v>
@@ -26479,7 +28415,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>83</v>
@@ -26499,7 +28435,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>83</v>
@@ -26519,13 +28455,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>53</v>
@@ -26539,7 +28475,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>83</v>
@@ -26559,7 +28495,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>83</v>
@@ -26586,7 +28522,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>83</v>
@@ -26613,7 +28549,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>83</v>
@@ -26626,7 +28562,7 @@
         <v>2.0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R72" s="1" t="s">
         <v>75</v>
@@ -26683,7 +28619,7 @@
         <v>4.0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="AN72" s="3">
         <v>0.0</v>
@@ -26715,7 +28651,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>92</v>
@@ -26735,7 +28671,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>92</v>
@@ -26755,7 +28691,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>92</v>
@@ -26775,7 +28711,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>92</v>
@@ -26795,7 +28731,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>92</v>
@@ -26818,7 +28754,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>92</v>
@@ -26847,7 +28783,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>92</v>
@@ -26913,7 +28849,7 @@
         <v>5.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="AN79" s="3">
         <v>1.0</v>
@@ -26945,7 +28881,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>98</v>
@@ -26965,7 +28901,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>98</v>
@@ -26985,7 +28921,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>98</v>
@@ -27008,13 +28944,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>51</v>
@@ -27031,7 +28967,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>98</v>
@@ -27094,7 +29030,7 @@
         <v>5.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="AN84" s="3">
         <v>0.0</v>
@@ -27126,7 +29062,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>106</v>
@@ -27146,13 +29082,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>53</v>
@@ -27166,7 +29102,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>106</v>
@@ -27189,7 +29125,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>106</v>
@@ -27212,7 +29148,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>106</v>
@@ -27221,7 +29157,7 @@
         <v>2.0</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>75</v>
@@ -27278,7 +29214,7 @@
         <v>2.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="AN89" s="3">
         <v>0.0</v>
@@ -27310,7 +29246,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>112</v>
@@ -27330,7 +29266,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>112</v>
@@ -27350,13 +29286,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>53</v>
@@ -27370,7 +29306,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>112</v>
@@ -27403,7 +29339,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>112</v>
@@ -27430,7 +29366,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>112</v>
@@ -27443,7 +29379,7 @@
         <v>1.0</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>54</v>
@@ -27497,7 +29433,7 @@
         <v>0.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="AN95" s="3">
         <v>1.0</v>
@@ -27529,7 +29465,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -27549,7 +29485,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -27569,13 +29505,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>53</v>
@@ -27589,7 +29525,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
@@ -27598,10 +29534,10 @@
         <v>54</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>124</v>
@@ -27609,7 +29545,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -27632,13 +29568,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>51</v>
@@ -27661,7 +29597,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>49</v>
@@ -27684,7 +29620,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>49</v>
@@ -27693,7 +29629,7 @@
         <v>4.0</v>
       </c>
       <c r="Q103" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>75</v>
@@ -27747,7 +29683,7 @@
         <v>14.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="AN103" s="3">
         <v>1.0</v>
@@ -27779,7 +29715,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>73</v>
@@ -27799,7 +29735,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>73</v>
@@ -27819,13 +29755,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>61</v>
@@ -27839,7 +29775,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>73</v>
@@ -27859,7 +29795,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>73</v>
@@ -27879,7 +29815,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>73</v>
@@ -27902,13 +29838,13 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>51</v>
@@ -27931,7 +29867,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>73</v>
@@ -27940,7 +29876,7 @@
         <v>3.0</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>75</v>
@@ -27994,7 +29930,7 @@
         <v>3.0</v>
       </c>
       <c r="AM111" s="1" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="AN111" s="3">
         <v>1.0</v>
@@ -28026,7 +29962,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>83</v>
@@ -28046,7 +29982,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>83</v>
@@ -28066,7 +30002,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>83</v>
@@ -28086,7 +30022,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>83</v>
@@ -28109,7 +30045,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>83</v>
@@ -28132,7 +30068,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>83</v>
@@ -28192,7 +30128,7 @@
         <v>5.0</v>
       </c>
       <c r="AM117" s="1" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="AN117" s="3">
         <v>0.0</v>
@@ -28224,7 +30160,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>92</v>
@@ -28244,7 +30180,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>92</v>
@@ -28264,7 +30200,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>92</v>
@@ -28284,7 +30220,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>92</v>
@@ -28304,7 +30240,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>92</v>
@@ -28327,7 +30263,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>92</v>
@@ -28356,7 +30292,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>92</v>
@@ -28419,7 +30355,7 @@
         <v>1.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="AN124" s="3">
         <v>1.0</v>
@@ -28451,7 +30387,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>98</v>
@@ -28471,13 +30407,13 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>53</v>
@@ -28491,7 +30427,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>98</v>
@@ -28514,13 +30450,13 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>98</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>51</v>
@@ -28543,7 +30479,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>98</v>
@@ -28552,7 +30488,7 @@
         <v>7.0</v>
       </c>
       <c r="Q129" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>75</v>
@@ -28606,7 +30542,7 @@
         <v>1.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="AN129" s="3">
         <v>1.0</v>
@@ -28638,13 +30574,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>53</v>
@@ -28658,7 +30594,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>106</v>
@@ -28678,7 +30614,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>106</v>
@@ -28701,7 +30637,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>106</v>
@@ -28761,7 +30697,7 @@
         <v>3.0</v>
       </c>
       <c r="AM133" s="1" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="AN133" s="3">
         <v>0.0</v>
@@ -28793,7 +30729,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>112</v>
@@ -28813,7 +30749,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>112</v>
@@ -28833,7 +30769,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>112</v>
@@ -28856,7 +30792,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>112</v>
@@ -28885,7 +30821,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>112</v>
@@ -28948,7 +30884,7 @@
         <v>6.0</v>
       </c>
       <c r="AM138" s="1" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="AN138" s="3">
         <v>1.0</v>
@@ -28980,7 +30916,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -29000,13 +30936,13 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>53</v>
@@ -29020,7 +30956,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -29040,13 +30976,13 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>51</v>
@@ -29060,7 +30996,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>49</v>
@@ -29083,7 +31019,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>49</v>
@@ -29106,7 +31042,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>49</v>
@@ -29166,7 +31102,7 @@
         <v>7.0</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="AN145" s="3">
         <v>0.0</v>
@@ -29198,7 +31134,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>73</v>
@@ -29218,7 +31154,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>73</v>
@@ -29238,13 +31174,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>53</v>
@@ -29258,7 +31194,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>73</v>
@@ -29273,7 +31209,7 @@
         <v>113</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>77</v>
@@ -29281,7 +31217,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>73</v>
@@ -29304,13 +31240,13 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>73</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>51</v>
@@ -29333,7 +31269,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>73</v>
@@ -29356,7 +31292,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>73</v>
@@ -29365,7 +31301,7 @@
         <v>2.0</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>75</v>
@@ -29451,7 +31387,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>83</v>
@@ -29471,7 +31407,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>83</v>
@@ -29491,13 +31427,13 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>61</v>
@@ -29511,7 +31447,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>83</v>
@@ -29534,7 +31470,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>83</v>
@@ -29557,7 +31493,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>83</v>
@@ -29577,7 +31513,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>83</v>
@@ -29586,7 +31522,7 @@
         <v>0.0</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="R160" s="1" t="s">
         <v>75</v>
@@ -29643,7 +31579,7 @@
         <v>0.0</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AN160" s="3">
         <v>0.0</v>
@@ -29675,7 +31611,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>92</v>
@@ -29695,7 +31631,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>92</v>
@@ -29707,7 +31643,7 @@
         <v>53</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>128</v>
@@ -29715,7 +31651,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>92</v>
@@ -29735,7 +31671,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>92</v>
@@ -29758,7 +31694,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>92</v>
@@ -29781,7 +31717,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>92</v>
@@ -29844,7 +31780,7 @@
         <v>1.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="AN166" s="3">
         <v>0.0</v>
@@ -29876,7 +31812,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>98</v>
@@ -29896,7 +31832,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>98</v>
@@ -29916,7 +31852,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>98</v>
@@ -29936,7 +31872,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>98</v>
@@ -29959,7 +31895,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>98</v>
@@ -30019,7 +31955,7 @@
         <v>0.0</v>
       </c>
       <c r="AM171" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="AN171" s="3">
         <v>0.0</v>
@@ -30051,7 +31987,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>106</v>
@@ -30063,7 +31999,7 @@
         <v>53</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>128</v>
@@ -30071,7 +32007,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>106</v>
@@ -30091,7 +32027,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>106</v>
@@ -30100,7 +32036,7 @@
         <v>108</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>95</v>
@@ -30111,7 +32047,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>106</v>
@@ -30134,7 +32070,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>106</v>
@@ -30157,13 +32093,13 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>106</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I177" s="2" t="s">
         <v>51</v>
@@ -30186,7 +32122,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>106</v>
@@ -30246,7 +32182,7 @@
         <v>0.0</v>
       </c>
       <c r="AM178" s="1" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="AN178" s="3">
         <v>1.0</v>
@@ -30278,7 +32214,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>112</v>
@@ -30298,7 +32234,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>112</v>
@@ -30318,7 +32254,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>112</v>
@@ -30341,13 +32277,13 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>112</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="I182" s="2" t="s">
         <v>51</v>
@@ -30370,7 +32306,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>112</v>
@@ -30399,7 +32335,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>112</v>
@@ -30453,7 +32389,7 @@
         <v>2.0</v>
       </c>
       <c r="AM184" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="AN184" s="3">
         <v>2.0</v>
@@ -30485,7 +32421,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>49</v>
@@ -30505,7 +32441,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>49</v>
@@ -30525,13 +32461,13 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>53</v>
@@ -30545,7 +32481,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>49</v>
@@ -30568,7 +32504,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>49</v>
@@ -30597,7 +32533,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>49</v>
@@ -30606,7 +32542,7 @@
         <v>1.0</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="S190" s="3">
         <v>20932.0</v>
@@ -30692,7 +32628,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>73</v>
@@ -30712,7 +32648,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>73</v>
@@ -30732,7 +32668,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>73</v>
@@ -30752,7 +32688,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>73</v>
@@ -30775,7 +32711,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>73</v>
@@ -30798,7 +32734,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>73</v>
@@ -30861,7 +32797,7 @@
         <v>3.0</v>
       </c>
       <c r="AM196" s="1" t="s">
-        <v>338</v>
+        <v>165</v>
       </c>
       <c r="AN196" s="3">
         <v>0.0</v>
